--- a/data/S1995_96_FINAL.xlsx
+++ b/data/S1995_96_FINAL.xlsx
@@ -24,8 +24,11 @@
     <sheet name="SERIES" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="CLUBS" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="META" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$14</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -33,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +51,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +78,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,12 +96,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -19316,7 +19334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19392,6 +19410,177 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1995_96_0260 'Kadaň B' prev→CLUB_S1994_95_0173 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1995_96_0390 'Vyškov B' prev→CLUB_S1994_95_0237 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1995_96_0414 'HC Poruba' prev→CLUB_S1994_95_0311 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1995_96_0423 'Frýdek Místek B' prev→CLUB_S1994_95_0063 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1995_96_0428 'Krnov B' prev→CLUB_S1994_95_0322 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1995_96_0015 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1995_96_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1995_96_0032 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1995_96_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1995_96_0034 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0021</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1995_96_0021 'Baráž o Extraligu' (L15, parent=NODE_S1995_96_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0027</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1995_96_0027 'Baráž o 1.ligu' (L20, parent=NODE_S1995_96_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0039</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1995_96_0039 'O postup do I.ligy' (L25, parent=NODE_S1995_96_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -23261,8 +23450,6 @@
         </is>
       </c>
     </row>
-    <row r="92"/>
-    <row r="93"/>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
@@ -23342,7 +23529,6 @@
         </is>
       </c>
     </row>
-    <row r="101"/>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
@@ -46524,6 +46710,347 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0260</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0260 'Kadaň B' prev→CLUB_S1994_95_0173 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0390</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0390 'Vyškov B' prev→CLUB_S1994_95_0237 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0414</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0414 'HC Poruba' prev→CLUB_S1994_95_0311 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0423</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0423 'Frýdek Místek B' prev→CLUB_S1994_95_0063 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0428</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0428 'Krnov B' prev→CLUB_S1994_95_0322 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0015</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0015 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0031</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0032</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0032 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0033</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0034</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0034 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0021</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1995_96_0021 'Baráž o Extraligu' (L15, parent=NODE_S1995_96_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0027</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1995_96_0027 'Baráž o 1.ligu' (L20, parent=NODE_S1995_96_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0039</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1995_96_0039 'O postup do I.ligy' (L25, parent=NODE_S1995_96_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1995_96_FINAL.xlsx
+++ b/data/S1995_96_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19334,7 +19334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19416,7 +19416,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1995_96_0260 'Kadaň B' prev→CLUB_S1994_95_0173 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -19428,7 +19428,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1995_96_0390 'Vyškov B' prev→CLUB_S1994_95_0237 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -19440,7 +19440,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1995_96_0414 'HC Poruba' prev→CLUB_S1994_95_0311 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -19452,7 +19452,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1995_96_0423 'Frýdek Místek B' prev→CLUB_S1994_95_0063 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -19464,7 +19464,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1995_96_0428 'Krnov B' prev→CLUB_S1994_95_0322 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19476,7 +19476,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1995_96_0015 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -19488,7 +19488,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1995_96_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -19500,7 +19500,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1995_96_0032 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -19512,7 +19512,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1995_96_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -19524,7 +19524,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1995_96_0034 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0307 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19534,14 +19534,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NODE_S1995_96_0021</t>
-        </is>
-      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1995_96_0021 'Baráž o Extraligu' (L15, parent=NODE_S1995_96_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0080 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19551,14 +19546,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NODE_S1995_96_0027</t>
-        </is>
-      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1995_96_0027 'Baráž o 1.ligu' (L20, parent=NODE_S1995_96_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0100 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -19568,17 +19558,420 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NODE_S1995_96_0039</t>
-        </is>
-      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1995_96_0039 'O postup do I.ligy' (L25, parent=NODE_S1995_96_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0107 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0173 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'IPF 90 Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0277 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0237 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0311 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0322 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Las Vegas Krnov' → 'Krnov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Newvers Rangers Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sport club Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Holešák Havlíčkův Brod' → 'Havlíčkův Brod' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -23450,6 +23843,8 @@
         </is>
       </c>
     </row>
+    <row r="92"/>
+    <row r="93"/>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
@@ -23480,6 +23875,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0001</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -23492,6 +23892,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0003</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -23504,6 +23909,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0003</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -23516,6 +23926,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0035</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -23529,6 +23944,7 @@
         </is>
       </c>
     </row>
+    <row r="101"/>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
@@ -25844,7 +26260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J471"/>
+  <dimension ref="A1:J472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -26019,12 +26435,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -26402,12 +26818,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -26533,12 +26949,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -26837,12 +27253,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -26879,12 +27295,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -27141,12 +27557,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -27781,12 +28197,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -27907,12 +28323,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -28510,12 +28926,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -32502,12 +32918,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -32544,12 +32960,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -33016,12 +33432,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -33236,12 +33652,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -33278,12 +33694,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -33498,12 +33914,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -33545,12 +33961,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -34648,12 +35064,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Tábor = Klub rozhodčích LH Tábor (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. Klub rozhodci ledniho hokeje. city Tábor.</t>
+          <t>Tábor = Klub rozhodčích LH Tábor (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. Klub rozhodci ledniho hokeje. city Tábor. || TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Klub rozhodčích LH Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -36595,12 +37011,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou. || TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Bižuterie Jablonec</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -36684,12 +37100,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -37161,12 +37577,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov.</t>
+          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov. || TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -38659,12 +39075,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>Pardubice = HC IPF 90 Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. Post-revolucni nazev. city Pardubice.</t>
+          <t>Pardubice = HC IPF 90 Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. Post-revolucni nazev. city Pardubice. || TBD: city 'IPF 90 Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>IPF 90 Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -39690,12 +40106,12 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -43020,12 +43436,12 @@
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -43067,12 +43483,12 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -44476,12 +44892,12 @@
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>Krnov = HC Las Vegas Krnov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Post-revolucni humorny nazev (USA mesto). city Krnov.</t>
+          <t>Krnov = HC Las Vegas Krnov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Post-revolucni humorny nazev (USA mesto). city Krnov. || TBD: city 'Las Vegas Krnov' → 'Krnov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>Las Vegas Krnov</t>
+          <t>Krnov</t>
         </is>
       </c>
     </row>
@@ -45079,12 +45495,12 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -45331,12 +45747,12 @@
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>Ostrava = HC Newvers Rangers Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Post-revolucni anglicky nazev. city Ostrava.</t>
+          <t>Ostrava = HC Newvers Rangers Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Post-revolucni anglicky nazev. city Ostrava. || TBD: city 'Newvers Rangers Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>Newvers Rangers Ostrava</t>
+          <t>Ostrava</t>
         </is>
       </c>
     </row>
@@ -45457,12 +45873,12 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>Ostrava = TJ NH Válcovny Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **NH** = Nová huť. **Válcovny** = oddeleni NH. city Ostrava.</t>
+          <t>Ostrava = TJ NH Válcovny Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **NH** = Nová huť. **Válcovny** = oddeleni NH. city Ostrava. || TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>NH Válcovny Ostrava</t>
+          <t>Ostrava</t>
         </is>
       </c>
     </row>
@@ -45583,12 +45999,12 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>Ostrava = Sport club Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. city Ostrava.</t>
+          <t>Ostrava = Sport club Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. city Ostrava. || TBD: city 'Sport club Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>Sport club Ostrava</t>
+          <t>Ostrava</t>
         </is>
       </c>
     </row>
@@ -46364,12 +46780,12 @@
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod = HBH Holešák Havlíčkův Brod (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **HBH Holešák** = post-revolucni nazev. city Havlíčkův Brod.</t>
+          <t>Havlíčkův Brod = HBH Holešák Havlíčkův Brod (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **HBH Holešák** = post-revolucni nazev. city Havlíčkův Brod. || TBD: city 'Holešák Havlíčkův Brod' → 'Havlíčkův Brod' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>Holešák Havlíčkův Brod</t>
+          <t>Havlíčkův Brod</t>
         </is>
       </c>
     </row>
@@ -46444,6 +46860,38 @@
       <c r="J471" t="inlineStr">
         <is>
           <t>Poděbrady</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0319</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>čtvrtfinále</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>čtvrtfinále</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -46720,11 +47168,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -46769,21 +47217,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0260</t>
+          <t>CLUB_S1995_96_0003</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0260 'Kadaň B' prev→CLUB_S1994_95_0173 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -46791,21 +47237,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0390</t>
+          <t>CLUB_S1995_96_0012</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0390 'Vyškov B' prev→CLUB_S1994_95_0237 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -46813,21 +47257,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0414</t>
+          <t>CLUB_S1995_96_0015</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0414 'HC Poruba' prev→CLUB_S1994_95_0311 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -46835,21 +47277,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0423</t>
+          <t>CLUB_S1995_96_0023</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0423 'Frýdek Místek B' prev→CLUB_S1994_95_0063 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -46857,21 +47297,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0428</t>
+          <t>CLUB_S1995_96_0024</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0428 'Krnov B' prev→CLUB_S1994_95_0322 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -46879,21 +47317,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0015</t>
+          <t>CLUB_S1995_96_0030</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0015 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -46901,21 +47337,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0031</t>
+          <t>CLUB_S1995_96_0047</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -46923,21 +47357,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0032</t>
+          <t>CLUB_S1995_96_0050</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0032 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -46945,21 +47377,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0033</t>
+          <t>CLUB_S1995_96_0066</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -46967,21 +47397,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0034</t>
+          <t>CLUB_S1995_96_0070</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0034 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0307 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -46989,21 +47417,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NODE_S1995_96_0021</t>
+          <t>CLUB_S1995_96_0075</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1995_96_0021 'Baráž o Extraligu' (L15, parent=NODE_S1995_96_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0080 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -47011,21 +47437,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NODE_S1995_96_0027</t>
+          <t>CLUB_S1995_96_0078</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1995_96_0027 'Baráž o 1.ligu' (L20, parent=NODE_S1995_96_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0100 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -47033,24 +47457,702 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NODE_S1995_96_0039</t>
+          <t>CLUB_S1995_96_0104</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1995_96_0039 'O postup do I.ligy' (L25, parent=NODE_S1995_96_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0107 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0159</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0159</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0160</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0171</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0176</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0177</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0182</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0183</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0207</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0255</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0256</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0258</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0260</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0173 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0262</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0266</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0269</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0303</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'IPF 90 Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0329</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0380</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0277 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0390</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0237 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0405</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0406</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0414</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0311 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0423</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0428</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0322 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0439</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Las Vegas Krnov' → 'Krnov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0453</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0459</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Newvers Rangers Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0462</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0465</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Sport club Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0483</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0483</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0484</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Holešák Havlíčkův Brod' → 'Havlíčkův Brod' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0319</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:F48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1995_96_FINAL.xlsx
+++ b/data/S1995_96_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2753,7 +2753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W90"/>
+  <dimension ref="A1:W89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8066,55 +8066,6 @@
       <c r="U89" s="3" t="n"/>
       <c r="V89" s="3" t="n"/>
       <c r="W89" s="3" t="inlineStr">
-        <is>
-          <t>skupina o 7.-10.místo</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="n"/>
-      <c r="C90" s="3" t="n"/>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>Dolní Bousov B – Sprint Jičín 0:3</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="n"/>
-      <c r="F90" s="3" t="n"/>
-      <c r="G90" s="3" t="n"/>
-      <c r="H90" s="3" t="n"/>
-      <c r="I90" s="3" t="n"/>
-      <c r="J90" s="3" t="n"/>
-      <c r="K90" s="3" t="n"/>
-      <c r="L90" s="3" t="n"/>
-      <c r="M90" s="3" t="n"/>
-      <c r="N90" s="3" t="n"/>
-      <c r="O90" s="3" t="n"/>
-      <c r="P90" s="3" t="inlineStr">
-        <is>
-          <t>L100</t>
-        </is>
-      </c>
-      <c r="Q90" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1995_96_0320</t>
-        </is>
-      </c>
-      <c r="R90" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0193</t>
-        </is>
-      </c>
-      <c r="S90" s="3" t="n"/>
-      <c r="T90" s="3" t="n"/>
-      <c r="U90" s="3" t="n"/>
-      <c r="V90" s="3" t="n"/>
-      <c r="W90" s="3" t="inlineStr">
         <is>
           <t>skupina o 7.-10.místo</t>
         </is>
@@ -19334,7 +19285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19416,7 +19367,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -19428,7 +19379,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -19440,7 +19391,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -19452,7 +19403,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -19464,7 +19415,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19476,7 +19427,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0307 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -19488,7 +19439,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0080 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -19500,7 +19451,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0100 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -19512,7 +19463,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0107 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -19524,7 +19475,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0307 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19536,7 +19487,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0080 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19548,7 +19499,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0100 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -19560,7 +19511,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0107 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -19572,7 +19523,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -19584,7 +19535,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -19596,7 +19547,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -19608,7 +19559,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -19620,7 +19571,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0173 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -19632,7 +19583,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -19644,7 +19595,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -19656,7 +19607,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -19668,7 +19619,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'IPF 90 Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -19680,7 +19631,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -19692,7 +19643,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0277 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -19704,7 +19655,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0237 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -19716,7 +19667,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0173 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -19728,7 +19679,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -19740,7 +19691,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0311 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -19752,7 +19703,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -19764,7 +19715,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'IPF 90 Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0322 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -19776,7 +19727,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Las Vegas Krnov' → 'Krnov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -19788,7 +19739,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0277 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Newvers Rangers Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -19800,7 +19751,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0237 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -19812,7 +19763,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sport club Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -19824,7 +19775,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -19836,7 +19787,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0311 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -19848,7 +19799,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Holešák Havlíčkův Brod' → 'Havlíčkův Brod' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -19860,118 +19811,10 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0322 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Las Vegas Krnov' → 'Krnov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Newvers Rangers Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sport club Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Holešák Havlíčkův Brod' → 'Havlíčkův Brod' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -19988,7 +19831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:L105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20047,6 +19890,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20089,6 +19937,11 @@
           <t>14 týmů (5 stat sloupců: W/WOT/D/LOT/L): základ + 1.kolo/QF/SF/finále/O3 + baráž. Mistr: HC Petra Vsetín.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20136,6 +19989,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20178,6 +20036,11 @@
           <t>1.liga: základní část + předkolo + čtvrtfinále + semifinále + baráž o 1.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20220,6 +20083,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20262,6 +20130,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20304,6 +20177,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20346,6 +20224,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20388,6 +20271,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20472,6 +20360,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0009</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20514,6 +20407,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0010</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -20556,6 +20454,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0011</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -20598,6 +20501,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0012</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -20640,6 +20548,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0013</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -20682,6 +20595,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0014</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -20724,6 +20642,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0015</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -20766,6 +20689,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0016</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -20808,6 +20736,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0017</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -20850,6 +20783,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0018</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -20892,6 +20830,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0019</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -20934,6 +20877,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0020</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -20976,6 +20924,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0021</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -21060,6 +21013,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0023</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -21102,6 +21060,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0024</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -21238,6 +21201,11 @@
           <t>Kvalifikace o 2.ligu. V kvalifikaci je první utkání hráno doma.</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0027</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -21280,6 +21248,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0028</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -21532,6 +21505,11 @@
           <t>II.liga: 2 skupiny + kvalifikace o 2.ligu.</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0031</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -21574,6 +21552,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0032</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -21616,6 +21599,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0033</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -21658,6 +21646,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0034</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -21742,6 +21735,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0036</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -21784,6 +21782,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0037</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -21952,6 +21955,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0036</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -22036,6 +22044,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0036</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -22204,6 +22217,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0041</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -22246,6 +22264,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0042</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -22288,6 +22311,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0043</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -22414,6 +22442,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0047</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -22456,6 +22489,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0048</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -22666,6 +22704,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0053</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -22708,6 +22751,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0054</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -22750,6 +22798,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0055</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -22792,6 +22845,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0056</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -22918,6 +22976,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0065</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -22960,6 +23023,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0066</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -23170,6 +23238,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0069</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -23212,6 +23285,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0070</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -23254,6 +23332,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0071</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -23296,6 +23379,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0072</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -23590,6 +23678,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0079</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -23632,6 +23725,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0080</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -23716,6 +23814,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0083</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -23758,6 +23861,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0084</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -23840,6 +23948,11 @@
       <c r="J91" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>NODE_S1994_95_0086</t>
         </is>
       </c>
     </row>
@@ -23863,6 +23976,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -23880,6 +23998,11 @@
           <t>NODE_S1995_96_0001</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -23897,6 +24020,11 @@
           <t>NODE_S1995_96_0003</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -23914,6 +24042,11 @@
           <t>NODE_S1995_96_0003</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -23931,6 +24064,11 @@
           <t>NODE_S1995_96_0035</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -23941,6 +24079,11 @@
       <c r="B100" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -26260,7 +26403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J472"/>
+  <dimension ref="A1:J471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -26435,12 +26578,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -26949,12 +27092,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -27557,12 +27700,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -28323,12 +28466,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -32918,12 +33061,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -32960,12 +33103,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -33432,12 +33575,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -33652,12 +33795,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -39767,64 +39910,59 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0320</t>
+          <t>CLUB_S1995_96_0323</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Dolní Bousov B – Sprint Jičín 0:3</t>
+          <t>Ytong Brno</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Dolní Bousov B – Sprint Jičín 0:3</t>
+          <t>Ytong Brno (N)</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>30_Východočeský</t>
+          <t>30_Jihomoravský</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>okresní</t>
-        </is>
-      </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>skupina o 7.-10.místo</t>
-        </is>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0193</t>
+          <t>L40</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>Sokol Dolní Bousov. city ✓. || Dolní Bousov (Wiki - registr ustavy 04/2026). Stredocesky kraj (okres Mlada Boleslav). city Dolní Bousov.</t>
+          <t>Po základní části změna názvu z HC Zetor Brno na HC Královopolská Brno. || ZJS Zbrojovka Spartak Brno (Závody Jana Švermy Zbrojovka Spartak Brno) — pokračovatel SK Židenice (1910). Historie: SK Židenice (1910, čtvrť Židenice) → fúze s SK Horácká Slavia Třebíč 1948 (prvoligová licence z Třebíče přišla do Brna!) → Sokol Zbrojovka Brno-Židenice → ZJS Zbrojovka Spartak Brno (1953) → zánik 1964. V 53/54: 1. liga sk. A, 3. místo. Domácí: ZS Za Lužánkami (10 200 div.). Stěhování Židenice → Ponava. JINÝ KLUB od Spartak Královo Pole. Zdroj: Wikipedie (D18). prev na 52/53 0010 ✓. || ZJS Zbrojovka Spartak Brno 53/54 (10_liga, oficiální nový název 1953). Zbrojovka Brno-Židenice (Wiki D18). Genealogie: SK Židenice (1910) → fúze 1948 s SK Horácká Slavia Třebíč → Sokol Zbrojovka Brno-Židenice (1948) → ZJS Zbrojovka Spartak Brno (1953) → ZÁNIK 1964. ZJS = Závody Jana Švermy, ZJŠ = pozdější varianta téhož. Domov ve čtvrti Židenice (původně), později Ponava. city Brno (D23, Židenice = čtvrť Brna). || Brno = HC Kometa Brno (Wiki D42 - registr ustavy 04/2026). Velka metropole, vice paralelnich klubu. HLAVNI chain HC Kometa Brno: ZSJ Zbrojovka -&gt; ZSJ Rude Hvezda (1953) -&gt; RH Brno -&gt; ZKL Brno -&gt; Kometa. Plus paralelni: Spartak Královopolská Brno (Královopolska strojirna), Spartak ZJŠ Brno (Závody Jana Švermy = Zbrojovka Brno), Tatran Brno (Bohunice/Žabovřesky/Židenice), Dukla Brno (vojensky), Lokomotiva Ingstav Brno, KZ Brno-Borovina je TŘEBÍČ, ne Brno! city Brno.</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>Dolní Bousov</t>
+          <t>Brno</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0323</t>
+          <t>CLUB_S1995_96_0324</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Ytong Brno</t>
+          <t>Spartak Nedvědice</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Ytong Brno (N)</t>
+          <t>Spartak Nedvědice</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -39832,41 +39970,41 @@
           <t>30_Jihomoravský</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F311" t="inlineStr">
         <is>
           <t>L40</t>
         </is>
       </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0223</t>
+        </is>
+      </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>Po základní části změna názvu z HC Zetor Brno na HC Královopolská Brno. || ZJS Zbrojovka Spartak Brno (Závody Jana Švermy Zbrojovka Spartak Brno) — pokračovatel SK Židenice (1910). Historie: SK Židenice (1910, čtvrť Židenice) → fúze s SK Horácká Slavia Třebíč 1948 (prvoligová licence z Třebíče přišla do Brna!) → Sokol Zbrojovka Brno-Židenice → ZJS Zbrojovka Spartak Brno (1953) → zánik 1964. V 53/54: 1. liga sk. A, 3. místo. Domácí: ZS Za Lužánkami (10 200 div.). Stěhování Židenice → Ponava. JINÝ KLUB od Spartak Královo Pole. Zdroj: Wikipedie (D18). prev na 52/53 0010 ✓. || ZJS Zbrojovka Spartak Brno 53/54 (10_liga, oficiální nový název 1953). Zbrojovka Brno-Židenice (Wiki D18). Genealogie: SK Židenice (1910) → fúze 1948 s SK Horácká Slavia Třebíč → Sokol Zbrojovka Brno-Židenice (1948) → ZJS Zbrojovka Spartak Brno (1953) → ZÁNIK 1964. ZJS = Závody Jana Švermy, ZJŠ = pozdější varianta téhož. Domov ve čtvrti Židenice (původně), později Ponava. city Brno (D23, Židenice = čtvrť Brna). || Brno = HC Kometa Brno (Wiki D42 - registr ustavy 04/2026). Velka metropole, vice paralelnich klubu. HLAVNI chain HC Kometa Brno: ZSJ Zbrojovka -&gt; ZSJ Rude Hvezda (1953) -&gt; RH Brno -&gt; ZKL Brno -&gt; Kometa. Plus paralelni: Spartak Královopolská Brno (Královopolska strojirna), Spartak ZJŠ Brno (Závody Jana Švermy = Zbrojovka Brno), Tatran Brno (Bohunice/Žabovřesky/Židenice), Dukla Brno (vojensky), Lokomotiva Ingstav Brno, KZ Brno-Borovina je TŘEBÍČ, ne Brno! city Brno.</t>
+          <t>Nedvědice = Spartak Nedvědice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov, dnes Vysocina). MEZ = Moravske elektrotechnicke zavody (Vsetin pobocka). city Nedvědice.</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>Brno</t>
+          <t>Nedvědice</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0324</t>
+          <t>CLUB_S1995_96_0325</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Spartak Nedvědice</t>
+          <t>Velká Bíteš</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Spartak Nedvědice</t>
+          <t>Velká Bíteš</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -39881,34 +40019,34 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0223</t>
+          <t>CLUB_S1994_95_0224</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>Nedvědice = Spartak Nedvědice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov, dnes Vysocina). MEZ = Moravske elektrotechnicke zavody (Vsetin pobocka). city Nedvědice.</t>
+          <t>Velká Bíteš = Sokol/Spartak Velká Bíteš (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Žďár nL Sazavou). city Velká Bíteš.</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>Nedvědice</t>
+          <t>Velká Bíteš</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0325</t>
+          <t>CLUB_S1995_96_0326</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Velká Bíteš</t>
+          <t>Blansko</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Velká Bíteš</t>
+          <t>Blansko</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -39923,34 +40061,34 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0224</t>
+          <t>CLUB_S1994_95_0226</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>Velká Bíteš = Sokol/Spartak Velká Bíteš (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Žďár nL Sazavou). city Velká Bíteš.</t>
+          <t>Blansko = Spartak DZ Blansko (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. DZ = podnik. city Blansko.</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>Velká Bíteš</t>
+          <t>Metra Blansko</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0326</t>
+          <t>CLUB_S1995_96_0327</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Blansko</t>
+          <t>Náměšť nad Oslavou</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Blansko</t>
+          <t>Náměšť nad Oslavou (N)</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -39958,6 +40096,11 @@
           <t>30_Jihomoravský</t>
         </is>
       </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F314" t="inlineStr">
         <is>
           <t>L40</t>
@@ -39965,34 +40108,34 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0226</t>
+          <t>CLUB_S1994_95_0229</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>Blansko = Spartak DZ Blansko (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. DZ = podnik. city Blansko.</t>
+          <t>Náměšť nad Oslavou = TJ Jiskra Náměšť (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Třebíč). **Náměšť nL Oslavou** = vyznamne **vojenske letiste** (zakladna 22. letecke zakladny). 'B' = druzstvo B. Zámek Náměšť nL Oslavou = národní kulturní pamatka (UNESCO). NE Náměšť na Hané (Severomoravsky/Olomoucko)! city Náměšť nad Oslavou.</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>Metra Blansko</t>
+          <t>Náměšť nad Oslavou</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0327</t>
+          <t>CLUB_S1995_96_0328</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Náměšť nad Oslavou</t>
+          <t>Boskovice</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Náměšť nad Oslavou (N)</t>
+          <t>Boskovice (N)</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -40012,34 +40155,34 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0229</t>
+          <t>CLUB_S1994_95_0235</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>Náměšť nad Oslavou = TJ Jiskra Náměšť (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Třebíč). **Náměšť nL Oslavou** = vyznamne **vojenske letiste** (zakladna 22. letecke zakladny). 'B' = druzstvo B. Zámek Náměšť nL Oslavou = národní kulturní pamatka (UNESCO). NE Náměšť na Hané (Severomoravsky/Olomoucko)! city Náměšť nad Oslavou.</t>
+          <t>Boskovice (Wiki - registr ustavy 04/2026). Jihomoravsky kraj. city Boskovice.</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>Náměšť nad Oslavou</t>
+          <t>Boskovice</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0328</t>
+          <t>CLUB_S1995_96_0329</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Boskovice</t>
+          <t>Slovácká Slavia Uherské Hradiště</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Boskovice (N)</t>
+          <t>Slovácká Slavia Uherské Hradiště</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -40047,11 +40190,6 @@
           <t>30_Jihomoravský</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F316" t="inlineStr">
         <is>
           <t>L40</t>
@@ -40059,34 +40197,34 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0235</t>
+          <t>CLUB_S1994_95_0222</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>Boskovice (Wiki - registr ustavy 04/2026). Jihomoravsky kraj. city Boskovice.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>Boskovice</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0329</t>
+          <t>CLUB_S1995_96_0330</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>VŠ Brno</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>VŠ Brno</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -40101,34 +40239,34 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0222</t>
+          <t>CLUB_S1994_95_0225</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>Brno = TJ VŠ Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VŠ** = Vysokoškolský klub (VUT/MU). city Brno.</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>Uherské Hradiště</t>
+          <t>VŠ Brno</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0330</t>
+          <t>CLUB_S1995_96_0331</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>VŠ Brno</t>
+          <t>Uherský Ostroh</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>VŠ Brno</t>
+          <t>Uherský Ostroh</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -40143,34 +40281,34 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0225</t>
+          <t>CLUB_S1994_95_0228</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>Brno = TJ VŠ Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VŠ** = Vysokoškolský klub (VUT/MU). city Brno.</t>
+          <t>TJ Tatran Uherský Ostroh. Oprava clean+city: "Uhersky" → "Uherský" (diakritika). prev k overeni Pavlem - mozny kandidat 55/56 0037 Tatran Uherský Ostroh (stejny clean!). || Uherský Ostroh = Tatran Uherský Ostroh (Wiki D42 - registr ustavy 04/2026). Jihomoravsky/Zlinsky kraj (okres Uherske Hradiste). Dyas = podnik. city Uherský Ostroh.</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>VŠ Brno</t>
+          <t>Uherský Ostroh</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0331</t>
+          <t>CLUB_S1995_96_0332</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Uherský Ostroh</t>
+          <t>HSK Vyškov</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Uherský Ostroh</t>
+          <t>HSK Vyškov (N)</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -40178,41 +40316,41 @@
           <t>30_Jihomoravský</t>
         </is>
       </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F319" t="inlineStr">
         <is>
           <t>L40</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0228</t>
-        </is>
-      </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>TJ Tatran Uherský Ostroh. Oprava clean+city: "Uhersky" → "Uherský" (diakritika). prev k overeni Pavlem - mozny kandidat 55/56 0037 Tatran Uherský Ostroh (stejny clean!). || Uherský Ostroh = Tatran Uherský Ostroh (Wiki D42 - registr ustavy 04/2026). Jihomoravsky/Zlinsky kraj (okres Uherske Hradiste). Dyas = podnik. city Uherský Ostroh.</t>
+          <t>Vyškov = HSK Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **HSK** = Hokejovy sportovni klub. city Vyškov.</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>Uherský Ostroh</t>
+          <t>HSK Vyškov</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0332</t>
+          <t>CLUB_S1995_96_0333</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>HSK Vyškov</t>
+          <t>Spartak Uherský Brod</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>HSK Vyškov (N)</t>
+          <t>Spartak Uherský Brod</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -40220,41 +40358,41 @@
           <t>30_Jihomoravský</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F320" t="inlineStr">
         <is>
           <t>L40</t>
         </is>
       </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0227</t>
+        </is>
+      </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>Vyškov = HSK Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **HSK** = Hokejovy sportovni klub. city Vyškov.</t>
+          <t>Smart fix prev: 52/53 0373 (Brno) → odstraněno (RH Uherský Brod v 52/53 neexistovala — nový klub v 53/54). city: → „Uherský Brod". || Oprava city: „Rudá Hvězda" → „Uherský Brod". prev na 52/53 0373 (RH Brno) byl chybný — odstraněno (RH Uherský Brod je nový v 53/54). || Sjednocení velikosti písmena: „Hvězda" → „hvězda" (Pavlovo rozhodnutí 04/2026 — jednotně malé „h" pro celý projekt). || Uherský Brod = HC Spartak Uherský Brod (Wiki - registr ustavy 04/2026). Jihomoravsky/Zlinsky kraj. liga. city Uherský Brod.</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>HSK Vyškov</t>
+          <t>Uherský Brod</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0333</t>
+          <t>CLUB_S1995_96_0334</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Spartak Uherský Brod</t>
+          <t>Tetčice</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Spartak Uherský Brod</t>
+          <t>Tetčice</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -40269,34 +40407,34 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0227</t>
+          <t>CLUB_S1994_95_0231</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>Smart fix prev: 52/53 0373 (Brno) → odstraněno (RH Uherský Brod v 52/53 neexistovala — nový klub v 53/54). city: → „Uherský Brod". || Oprava city: „Rudá Hvězda" → „Uherský Brod". prev na 52/53 0373 (RH Brno) byl chybný — odstraněno (RH Uherský Brod je nový v 53/54). || Sjednocení velikosti písmena: „Hvězda" → „hvězda" (Pavlovo rozhodnutí 04/2026 — jednotně malé „h" pro celý projekt). || Uherský Brod = HC Spartak Uherský Brod (Wiki - registr ustavy 04/2026). Jihomoravsky/Zlinsky kraj. liga. city Uherský Brod.</t>
+          <t>Tetčice = TJ Sokol Tetčice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). city Tetčice.</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>Uherský Brod</t>
+          <t>Tetčice</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0334</t>
+          <t>CLUB_S1995_96_0335</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Tetčice</t>
+          <t>HAS Jihlava</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Tetčice</t>
+          <t>HAS Jihlava</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -40311,34 +40449,34 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0231</t>
+          <t>CLUB_S1994_95_0232</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>Tetčice = TJ Sokol Tetčice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). city Tetčice.</t>
+          <t>Jihlava = HAS Jihlava (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **HAS** = pravdepodobne Hokejovy ASociacni klub. city Jihlava.</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>Tetčice</t>
+          <t>HAS Jihlava</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0335</t>
+          <t>CLUB_S1995_96_0336</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>HAS Jihlava</t>
+          <t>Telč</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>HAS Jihlava</t>
+          <t>Telč</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -40353,34 +40491,34 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0232</t>
+          <t>CLUB_S1994_95_0230</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>Jihlava = HAS Jihlava (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **HAS** = pravdepodobne Hokejovy ASociacni klub. city Jihlava.</t>
+          <t>Oprava city: závodní „Motorpal" → „Telč". || Motorpal Telč 52/53 (20_Jihlavský). KLÍČOVÝ ROK - patronat podniku Motorpal (vstrikovaci systemy). Telč = SK Telč / Rytíři z Telče (Wiki D42 - Pavlovo 04/2026). Sokol Telč (49/50) -&gt; Motorpal Telč (52/53, podnik Motorpal - vyroba dieselovych vstrikovacich systemu) -&gt; Spartak Telč (53/54+, DSO reforma) -&gt; SK Telč -&gt; Rytíři z Telče (dnes). city Telč. || Motorpal Telč 52/53 (20_Jihlavský). KLÍČOVÝ ROK - patronat Motorpal (vstrikovaci systemy). Telč = SK Telč / Rytíři z Telče (Wiki D42 - Pavlovo 04/2026). Sokol -&gt; Motorpal (52/53) -&gt; Spartak (53/54+, DSO) -&gt; SK Telč. city Telč. || Telč = HC Telč (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. Hlavni chain: Sokol Telč -&gt; Spartak Telč -&gt; Motorpal Telč (vstrikovaci system) -&gt; HC Telč. UNESCO mesto. city Telč.</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>HAS Jihlava</t>
+          <t>Telč</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0336</t>
+          <t>CLUB_S1995_96_0337</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Telč</t>
+          <t>Náměšť nad Oslavou B</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Telč</t>
+          <t>Náměšť nad Oslavou B  (N)</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -40388,6 +40526,11 @@
           <t>30_Jihomoravský</t>
         </is>
       </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F324" t="inlineStr">
         <is>
           <t>L40</t>
@@ -40395,34 +40538,34 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0230</t>
+          <t>CLUB_S1994_95_0279</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>Oprava city: závodní „Motorpal" → „Telč". || Motorpal Telč 52/53 (20_Jihlavský). KLÍČOVÝ ROK - patronat podniku Motorpal (vstrikovaci systemy). Telč = SK Telč / Rytíři z Telče (Wiki D42 - Pavlovo 04/2026). Sokol Telč (49/50) -&gt; Motorpal Telč (52/53, podnik Motorpal - vyroba dieselovych vstrikovacich systemu) -&gt; Spartak Telč (53/54+, DSO reforma) -&gt; SK Telč -&gt; Rytíři z Telče (dnes). city Telč. || Motorpal Telč 52/53 (20_Jihlavský). KLÍČOVÝ ROK - patronat Motorpal (vstrikovaci systemy). Telč = SK Telč / Rytíři z Telče (Wiki D42 - Pavlovo 04/2026). Sokol -&gt; Motorpal (52/53) -&gt; Spartak (53/54+, DSO) -&gt; SK Telč. city Telč. || Telč = HC Telč (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. Hlavni chain: Sokol Telč -&gt; Spartak Telč -&gt; Motorpal Telč (vstrikovaci system) -&gt; HC Telč. UNESCO mesto. city Telč.</t>
+          <t>Náměšť nad Oslavou = TJ Jiskra Náměšť nL Oslavou B (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. 'B' = druzstvo B. city Náměšť nad Oslavou.</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>Telč</t>
+          <t>Náměšť nad Oslavou B</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0337</t>
+          <t>CLUB_S1995_96_0338</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Náměšť nad Oslavou B</t>
+          <t>Nová Říše</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Náměšť nad Oslavou B  (N)</t>
+          <t>Nová Říše</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -40430,11 +40573,6 @@
           <t>30_Jihomoravský</t>
         </is>
       </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F325" t="inlineStr">
         <is>
           <t>L40</t>
@@ -40442,34 +40580,34 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0279</t>
+          <t>CLUB_S1994_95_0244</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>Náměšť nad Oslavou = TJ Jiskra Náměšť nL Oslavou B (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. 'B' = druzstvo B. city Náměšť nad Oslavou.</t>
+          <t>Nová Říše = TJ Nová Říše (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Jihlava). **Nová Říše** = premonstratský klášter (12. st.). city Nová Říše.</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>Náměšť nad Oslavou B</t>
+          <t>Nová Říše</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0338</t>
+          <t>CLUB_S1995_96_0339</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Nová Říše</t>
+          <t>Popůvky</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Nová Říše</t>
+          <t>Popůvky</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -40484,34 +40622,34 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0244</t>
+          <t>CLUB_S1994_95_0245</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>Nová Říše = TJ Nová Říše (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Jihlava). **Nová Říše** = premonstratský klášter (12. st.). city Nová Říše.</t>
+          <t>Popůvky = TJ Sokol Popůvky (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). city Popůvky.</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>Nová Říše</t>
+          <t>Popůvky</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0339</t>
+          <t>CLUB_S1995_96_0340</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Popůvky</t>
+          <t>Avia Brno</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Popůvky</t>
+          <t>Avia Brno</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -40524,36 +40662,31 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0245</t>
-        </is>
-      </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>Popůvky = TJ Sokol Popůvky (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). city Popůvky.</t>
+          <t>Brno = HC Avia Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **Avia** = letadla. city Brno.</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>Popůvky</t>
+          <t>Avia Brno</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0340</t>
+          <t>CLUB_S1995_96_0341</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Avia Brno</t>
+          <t>Březina</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Avia Brno</t>
+          <t>Březina</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -40566,31 +40699,36 @@
           <t>L40</t>
         </is>
       </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0255</t>
+        </is>
+      </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>Brno = HC Avia Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **Avia** = letadla. city Brno.</t>
+          <t>Březina u Tišnova = TJ Sokol Březina (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). POZOR: vícero - Březina u Tišnova (Brno-venkov), Březina u Boskovic (Blansko). K overeni. city Březina u Tišnova.</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>Avia Brno</t>
+          <t>Březina</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0341</t>
+          <t>CLUB_S1995_96_0342</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Březina</t>
+          <t>Bulldogs Brno</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Březina</t>
+          <t>Bulldogs Brno (N)</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -40598,41 +40736,41 @@
           <t>30_Jihomoravský</t>
         </is>
       </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F329" t="inlineStr">
         <is>
           <t>L40</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0255</t>
-        </is>
-      </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>Březina u Tišnova = TJ Sokol Březina (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). POZOR: vícero - Březina u Tišnova (Brno-venkov), Březina u Boskovic (Blansko). K overeni. city Březina u Tišnova.</t>
+          <t>Brno = HC Bulldogs Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Post-revolucni anglicky nazev. city Brno.</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>Březina</t>
+          <t>Bulldogs Brno</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0342</t>
+          <t>CLUB_S1995_96_0343</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Bulldogs Brno</t>
+          <t>Lysice</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Bulldogs Brno (N)</t>
+          <t>Lysice</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -40640,41 +40778,41 @@
           <t>30_Jihomoravský</t>
         </is>
       </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F330" t="inlineStr">
         <is>
           <t>L40</t>
         </is>
       </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0239</t>
+        </is>
+      </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>Brno = HC Bulldogs Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Post-revolucni anglicky nazev. city Brno.</t>
+          <t>Lysice = Sokol Lysice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Blansko). city Lysice.</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>Bulldogs Brno</t>
+          <t>Lysice</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0343</t>
+          <t>CLUB_S1995_96_0344</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Lysice</t>
+          <t>Nedvědice B</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Lysice</t>
+          <t>Nedvědice B</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -40689,34 +40827,34 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0239</t>
+          <t>CLUB_S1994_95_0251</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>Lysice = Sokol Lysice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Blansko). city Lysice.</t>
+          <t>Nedvědice = Spartak Nedvědice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov, dnes Vysocina). MEZ = Moravske elektrotechnicke zavody (Vsetin pobocka). city Nedvědice.</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>Lysice</t>
+          <t>Nedvědice</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0344</t>
+          <t>CLUB_S1995_96_0345</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Nedvědice B</t>
+          <t>Rájec</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Nedvědice B</t>
+          <t>Rájec</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -40729,36 +40867,31 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0251</t>
-        </is>
-      </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>Nedvědice = Spartak Nedvědice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov, dnes Vysocina). MEZ = Moravske elektrotechnicke zavody (Vsetin pobocka). city Nedvědice.</t>
+          <t>Rájec nL Svitavou = Tatran Rájec nL Svitavou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Blansko). city Rájec nad Svitavou.</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>Nedvědice</t>
+          <t>Rájec</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0345</t>
+          <t>CLUB_S1995_96_0346</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Rájec</t>
+          <t>Řečice</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Rájec</t>
+          <t>Řečice</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -40771,31 +40904,36 @@
           <t>L40</t>
         </is>
       </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0234</t>
+        </is>
+      </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>Rájec nL Svitavou = Tatran Rájec nL Svitavou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Blansko). city Rájec nad Svitavou.</t>
+          <t>Řečice u Žďáru = TJ Sokol Řečice (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Žďár nL Sázavou, district 'Žďár nL Sázavou' potvrzen). POZOR: vícero Řečic - Velká Řečice u Pelhřimova, Mala Řečice. K overeni. city Řečice u Žďáru nad Sázavou.</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>Rájec</t>
+          <t>Řečice</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0346</t>
+          <t>CLUB_S1995_96_0347</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Řečice</t>
+          <t>Dl.Brtnice</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Řečice</t>
+          <t>Dl.Brtnice</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -40810,34 +40948,34 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0234</t>
+          <t>CLUB_S1994_95_0271</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>Řečice u Žďáru = TJ Sokol Řečice (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Žďár nL Sázavou, district 'Žďár nL Sázavou' potvrzen). POZOR: vícero Řečic - Velká Řečice u Pelhřimova, Mala Řečice. K overeni. city Řečice u Žďáru nad Sázavou.</t>
+          <t>Dlouhá Brtnice = TJ Sokol Dlouhá Brtnice (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Jihlava). city Dlouhá Brtnice.</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>Řečice</t>
+          <t>Dlouhá Brtnice</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0347</t>
+          <t>CLUB_S1995_96_0348</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Dl.Brtnice</t>
+          <t>Čechočovice</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Dl.Brtnice</t>
+          <t>Čechočovice</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -40852,34 +40990,34 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0271</t>
+          <t>CLUB_S1994_95_0233</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>Dlouhá Brtnice = TJ Sokol Dlouhá Brtnice (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Jihlava). city Dlouhá Brtnice.</t>
+          <t>Čechočovice = Sokol Čechočovice (Wiki D42 - registr ustavy 04/2026). Vysocina kraj (okres Třebíč). city Čechočovice. || Vladislav = Sokol/Jiskra Vladislav (Wiki D42 - registr ustavy 04/2026). Vysocina kraj (okres Třebíč). 'Vladislav' jako jmenowy nazev. city Vladislav.</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>Dlouhá Brtnice</t>
+          <t>Čechočovice</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0348</t>
+          <t>CLUB_S1995_96_0349</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Čechočovice</t>
+          <t>Velké Meziříčí</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Čechočovice</t>
+          <t>Velké Meziříčí</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -40894,34 +41032,34 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0233</t>
+          <t>CLUB_S1994_95_0246</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>Čechočovice = Sokol Čechočovice (Wiki D42 - registr ustavy 04/2026). Vysocina kraj (okres Třebíč). city Čechočovice. || Vladislav = Sokol/Jiskra Vladislav (Wiki D42 - registr ustavy 04/2026). Vysocina kraj (okres Třebíč). 'Vladislav' jako jmenowy nazev. city Vladislav.</t>
+          <t>Sokol Velké Meziříčí. Jiný klub od 0484 (CLUB_S1954_55_0484 bez prefixu). || Sokol Velké Meziříčí 54/55 (30_Jihlavský). Velké Meziříčí = HHK Velké Meziříčí (Wiki D42 - Pavlovo 04/2026). Velké Meziříčí (50/51-) -&gt; Sokol Velké Meziříčí (54/55) -&gt; Spartak Velké Meziříčí (56/57+, DSO reforma) -&gt; kontinuita -&gt; HHK Velké Meziříčí. Patterns: Velké Meziříčí, Sokol VM, Spartak VM. POZOR: 50/51 0731 'České Meziříčí' je JINE MESTO (Královéhradecký). Tatran Valašské Meziříčí je tez JINE MESTO (Gottwaldovský/Zlinsky). city Velké Meziříčí. || Sokol Velké Meziříčí 54/55 (30_Jihlavský). Velké Meziříčí = HHK VM (Wiki D42 - Pavlovo 04/2026). Sokol VM -&gt; Spartak VM (56/57+). NE České ani Valašské Meziříčí. city Velké Meziříčí. || Velké Meziříčí = Spartak/HC Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. POZOR: NE Valašské Meziříčí (Severomoravsky/Zlinsky)! city Velké Meziříčí.</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>Čechočovice</t>
+          <t>Velké Meziříčí</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0349</t>
+          <t>CLUB_S1995_96_0350</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Velké Meziříčí</t>
+          <t>Pavlice</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Velké Meziříčí</t>
+          <t>Pavlice (N)</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -40929,6 +41067,11 @@
           <t>30_Jihomoravský</t>
         </is>
       </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F337" t="inlineStr">
         <is>
           <t>L40</t>
@@ -40936,34 +41079,34 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0246</t>
+          <t>CLUB_S1994_95_0296</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>Sokol Velké Meziříčí. Jiný klub od 0484 (CLUB_S1954_55_0484 bez prefixu). || Sokol Velké Meziříčí 54/55 (30_Jihlavský). Velké Meziříčí = HHK Velké Meziříčí (Wiki D42 - Pavlovo 04/2026). Velké Meziříčí (50/51-) -&gt; Sokol Velké Meziříčí (54/55) -&gt; Spartak Velké Meziříčí (56/57+, DSO reforma) -&gt; kontinuita -&gt; HHK Velké Meziříčí. Patterns: Velké Meziříčí, Sokol VM, Spartak VM. POZOR: 50/51 0731 'České Meziříčí' je JINE MESTO (Královéhradecký). Tatran Valašské Meziříčí je tez JINE MESTO (Gottwaldovský/Zlinsky). city Velké Meziříčí. || Sokol Velké Meziříčí 54/55 (30_Jihlavský). Velké Meziříčí = HHK VM (Wiki D42 - Pavlovo 04/2026). Sokol VM -&gt; Spartak VM (56/57+). NE České ani Valašské Meziříčí. city Velké Meziříčí. || Velké Meziříčí = Spartak/HC Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. POZOR: NE Valašské Meziříčí (Severomoravsky/Zlinsky)! city Velké Meziříčí.</t>
+          <t>Pavlice = TJ Sokol Pavlice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). 'ZNO' = Znojmo skupina. city Pavlice.</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>Velké Meziříčí</t>
+          <t>Pavlice</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0350</t>
+          <t>CLUB_S1995_96_0351</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Pavlice</t>
+          <t>Domašov</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Pavlice (N)</t>
+          <t>Domašov</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -40971,11 +41114,6 @@
           <t>30_Jihomoravský</t>
         </is>
       </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F338" t="inlineStr">
         <is>
           <t>L40</t>
@@ -40983,34 +41121,34 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0296</t>
+          <t>CLUB_S1994_95_0248</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>Pavlice = TJ Sokol Pavlice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). 'ZNO' = Znojmo skupina. city Pavlice.</t>
+          <t>Domašov u Brna = TJ Sokol Domašov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). city Domašov u Brna.</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>Pavlice</t>
+          <t>Domašov</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0351</t>
+          <t>CLUB_S1995_96_0352</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Domašov</t>
+          <t>Madlov</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Domašov</t>
+          <t>Madlov</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -41023,36 +41161,31 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0248</t>
-        </is>
-      </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>Domašov u Brna = TJ Sokol Domašov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). city Domašov u Brna.</t>
+          <t>Madlov = TJ Sokol Madlov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. POZOR: nelze identifikovat. K UPRESNENI. city Madlov.</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>Domašov</t>
+          <t>Madlov</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0352</t>
+          <t>CLUB_S1995_96_0353</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Madlov</t>
+          <t>Velká Bíteš B</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Madlov</t>
+          <t>Velká Bíteš B</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -41065,31 +41198,36 @@
           <t>L40</t>
         </is>
       </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0249</t>
+        </is>
+      </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>Madlov = TJ Sokol Madlov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. POZOR: nelze identifikovat. K UPRESNENI. city Madlov.</t>
+          <t>Velká Bíteš = Sokol/Spartak Velká Bíteš (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Žďár nL Sazavou). city Velká Bíteš.</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>Madlov</t>
+          <t>Velká Bíteš</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0353</t>
+          <t>CLUB_S1995_96_0354</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Velká Bíteš B</t>
+          <t>Veverská Bitýška</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Velká Bíteš B</t>
+          <t>Veverská Bitýška</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -41104,34 +41242,34 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0249</t>
+          <t>CLUB_S1994_95_0240</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>Velká Bíteš = Sokol/Spartak Velká Bíteš (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Žďár nL Sazavou). city Velká Bíteš.</t>
+          <t>Veverská Bítýška = TJ Sokol Veverská Bítýška (Wiki D42 - registr ustavy 04/2026). PARSING CHYBA: 'Bitýška' = preklep z 'Bítýška'. Jihomoravsky kraj (okres Brno-venkov). city Veverská Bítýška.</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>Velká Bíteš</t>
+          <t>Veverská Bitýška</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0354</t>
+          <t>CLUB_S1995_96_0355</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Veverská Bitýška</t>
+          <t>Vír</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Veverská Bitýška</t>
+          <t>Vír (N)</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -41139,6 +41277,11 @@
           <t>30_Jihomoravský</t>
         </is>
       </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F342" t="inlineStr">
         <is>
           <t>L40</t>
@@ -41146,34 +41289,34 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0240</t>
+          <t>CLUB_S1994_95_0298</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>Veverská Bítýška = TJ Sokol Veverská Bítýška (Wiki D42 - registr ustavy 04/2026). PARSING CHYBA: 'Bitýška' = preklep z 'Bítýška'. Jihomoravsky kraj (okres Brno-venkov). city Veverská Bítýška.</t>
+          <t>Vír = TJ Jiskra/Sokol Vír (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Žďár nL Sázavou). Patterns: Sokol Vír -&gt; Jiskra Vír. city Vír.</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>Veverská Bitýška</t>
+          <t>Vír</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0355</t>
+          <t>CLUB_S1995_96_0356</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Vír</t>
+          <t>Vilémovice</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Vír (N)</t>
+          <t>Vilémovice (N)</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -41193,34 +41336,34 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0298</t>
+          <t>CLUB_S1994_95_0259</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>Vír = TJ Jiskra/Sokol Vír (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Žďár nL Sázavou). Patterns: Sokol Vír -&gt; Jiskra Vír. city Vír.</t>
+          <t>Vilémovice u Macochy = TJ Sokol Vilémovice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Blansko). **Moravsky kras** - blizko Macochy. POZOR: NE Vilémovice u Havlíčkova Brodu (Vysocina), NE Vilémovice u Ledce. city Vilémovice u Macochy.</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>Vír</t>
+          <t>Vilémovice</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0356</t>
+          <t>CLUB_S1995_96_0357</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Vilémovice</t>
+          <t>Černá Hora</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Vilémovice (N)</t>
+          <t>Černá Hora</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -41228,11 +41371,6 @@
           <t>30_Jihomoravský</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F344" t="inlineStr">
         <is>
           <t>L40</t>
@@ -41240,34 +41378,34 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0259</t>
+          <t>CLUB_S1994_95_0253</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>Vilémovice u Macochy = TJ Sokol Vilémovice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Blansko). **Moravsky kras** - blizko Macochy. POZOR: NE Vilémovice u Havlíčkova Brodu (Vysocina), NE Vilémovice u Ledce. city Vilémovice u Macochy.</t>
+          <t>Černá Hora = Slavoj/Sokol Černá Hora (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Blansko). Mesto pivovaru. city Černá Hora.</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>Vilémovice</t>
+          <t>Černá Hora</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0357</t>
+          <t>CLUB_S1995_96_0358</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Černá Hora</t>
+          <t>Hrušky</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Černá Hora</t>
+          <t>Hrušky</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -41282,34 +41420,34 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0253</t>
+          <t>CLUB_S1994_95_0236</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>Černá Hora = Slavoj/Sokol Černá Hora (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Blansko). Mesto pivovaru. city Černá Hora.</t>
+          <t>Hrušky = TJ Tatran Hrušky (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Břeclav). NE Hrušky u Vyškova! city Hrušky u Břeclavi.</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>Černá Hora</t>
+          <t>Hrušky</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0358</t>
+          <t>CLUB_S1995_96_0359</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Hrušky</t>
+          <t>Technika Brno</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Hrušky</t>
+          <t>Technika Brno (N)</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -41317,6 +41455,11 @@
           <t>30_Jihomoravský</t>
         </is>
       </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F346" t="inlineStr">
         <is>
           <t>L40</t>
@@ -41324,34 +41467,34 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0236</t>
+          <t>CLUB_S1994_95_0261</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>Hrušky = TJ Tatran Hrušky (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Břeclav). NE Hrušky u Vyškova! city Hrušky u Břeclavi.</t>
+          <t>Brno = TJ Slavia Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **Slavia Technika Brno** = vysokoskolsky klub VUT Brno. city Brno.</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>Hrušky</t>
+          <t>Technika Brno</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0359</t>
+          <t>CLUB_S1995_96_0360</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Technika Brno</t>
+          <t>SKP Kroměříž</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Technika Brno (N)</t>
+          <t>SKP Kroměříž (N)</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -41371,34 +41514,34 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0261</t>
+          <t>CLUB_S1994_95_0272</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>Brno = TJ Slavia Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **Slavia Technika Brno** = vysokoskolsky klub VUT Brno. city Brno.</t>
+          <t>B-tym Spartak Kroměříž (PAL = závod). clean: II -&gt; B. Oprava city: "PAL Kroměříž" -&gt; "Kroměříž". || Kroměříž = HK Kroměříž (Wiki - registr ustavy 04/2026). Severomoravsky/Zlinsky kraj. Mestske vyznamne - HK Kromeriz Patterns: PAL Kroměříž (podnik), HK Kromeriz. city Kroměříž.</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>Technika Brno</t>
+          <t>Kroměříž</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0360</t>
+          <t>CLUB_S1995_96_0361</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>SKP Kroměříž</t>
+          <t>Ivanovice na Hané</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>SKP Kroměříž (N)</t>
+          <t>Ivanovice na Hané</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -41406,11 +41549,6 @@
           <t>30_Jihomoravský</t>
         </is>
       </c>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F348" t="inlineStr">
         <is>
           <t>L40</t>
@@ -41418,34 +41556,34 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0272</t>
+          <t>CLUB_S1994_95_0254</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>B-tym Spartak Kroměříž (PAL = závod). clean: II -&gt; B. Oprava city: "PAL Kroměříž" -&gt; "Kroměříž". || Kroměříž = HK Kroměříž (Wiki - registr ustavy 04/2026). Severomoravsky/Zlinsky kraj. Mestske vyznamne - HK Kromeriz Patterns: PAL Kroměříž (podnik), HK Kromeriz. city Kroměříž.</t>
+          <t>Ivanovice na Hané = TJ Slovan Ivanovice na Hané (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (okres Vyškov, district '(VYŠ)' potvrzen). **Ivanovice na Hané** = mestyste, slozite spojeni Hane. city Ivanovice na Hané.</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>Kroměříž</t>
+          <t>Ivanovice na Hané</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0361</t>
+          <t>CLUB_S1995_96_0363</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Ivanovice na Hané</t>
+          <t>Sloup</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Ivanovice na Hané</t>
+          <t>Sloup</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -41455,39 +41593,44 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>L40</t>
+          <t>okresní</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Blansko</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0254</t>
+          <t>CLUB_S1994_95_0257</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>Ivanovice na Hané = TJ Slovan Ivanovice na Hané (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (okres Vyškov, district '(VYŠ)' potvrzen). **Ivanovice na Hané** = mestyste, slozite spojeni Hane. city Ivanovice na Hané.</t>
+          <t>Sloup v Moravském krasu = TJ Sokol Sloup (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Blansko). Sloupsko-šošůvské jeskyně. NE Sloup v Cechach (Severocesky). city Sloup v Moravském krasu.</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>Ivanovice na Hané</t>
+          <t>Sloup</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0363</t>
+          <t>CLUB_S1995_96_0364</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Sloup</t>
+          <t>Bořitov</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Sloup</t>
+          <t>Bořitov</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -41507,34 +41650,34 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0257</t>
+          <t>CLUB_S1994_95_0258</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>Sloup v Moravském krasu = TJ Sokol Sloup (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Blansko). Sloupsko-šošůvské jeskyně. NE Sloup v Cechach (Severocesky). city Sloup v Moravském krasu.</t>
+          <t>Bořitov = TJ Sokol Bořitov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Blansko). city Bořitov.</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>Sloup</t>
+          <t>Bořitov</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0364</t>
+          <t>CLUB_S1995_96_0365</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Bořitov</t>
+          <t>Kunštát</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Bořitov</t>
+          <t>Kunštát</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -41554,34 +41697,34 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0258</t>
+          <t>CLUB_S1994_95_0260</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>Bořitov = TJ Sokol Bořitov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Blansko). city Bořitov.</t>
+          <t>Kunštát = TJ Sokol Kunštát (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Blansko). city Kunštát.</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>Bořitov</t>
+          <t>Kunštát</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0365</t>
+          <t>CLUB_S1995_96_0366</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Kunštát</t>
+          <t>Bulldogs Brno B</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Kunštát</t>
+          <t>Bulldogs Brno B</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -41596,39 +41739,34 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Blansko</t>
-        </is>
-      </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0260</t>
+          <t>Brno venkov + Brno město</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>Kunštát = TJ Sokol Kunštát (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Blansko). city Kunštát.</t>
+          <t>Brno = HC Bulldogs Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Post-revolucni anglicky nazev. city Brno.</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>Kunštát</t>
+          <t>Bulldogs Brno B</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0366</t>
+          <t>CLUB_S1995_96_0367</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Bulldogs Brno B</t>
+          <t>Lelekovice</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Bulldogs Brno B</t>
+          <t>Lelekovice</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -41646,31 +41784,36 @@
           <t>Brno venkov + Brno město</t>
         </is>
       </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0264</t>
+        </is>
+      </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>Brno = HC Bulldogs Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Post-revolucni anglicky nazev. city Brno.</t>
+          <t>Lelekovice = TJ Sokol Lelekovice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). NE Lelkovice. city Lelekovice.</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>Bulldogs Brno B</t>
+          <t>Lelekovice</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0367</t>
+          <t>CLUB_S1995_96_0368</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Lelekovice</t>
+          <t>Starý Lískovec (BM)</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Lelekovice</t>
+          <t>Starý Lískovec (BM)</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -41690,34 +41833,34 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0264</t>
+          <t>CLUB_S1994_95_0266</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>Lelekovice = TJ Sokol Lelekovice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). NE Lelkovice. city Lelekovice.</t>
+          <t>Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha. || Brno = drobne brnenske kluby (Wiki D42 - registr ustavy 04/2026). Stadion Lískovec, I. Brnenska, Spartak Spalovny atd. = paralelni kluby. I. Brněnská = puvodni Brno I. PHN = paralelni hokejovy nazev. city Brno.</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>Lelekovice</t>
+          <t>Starý Lískovec</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0368</t>
+          <t>CLUB_S1995_96_0369</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Starý Lískovec (BM)</t>
+          <t>Šerkovice</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Starý Lískovec (BM)</t>
+          <t>Šerkovice</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -41737,34 +41880,34 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0266</t>
+          <t>CLUB_S1994_95_0263</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha. || Brno = drobne brnenske kluby (Wiki D42 - registr ustavy 04/2026). Stadion Lískovec, I. Brnenska, Spartak Spalovny atd. = paralelni kluby. I. Brněnská = puvodni Brno I. PHN = paralelni hokejovy nazev. city Brno.</t>
+          <t>Šerkovice = TJ Sokol Šerkovice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Blansko). city Šerkovice.</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>Starý Lískovec</t>
+          <t>Šerkovice</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0369</t>
+          <t>CLUB_S1995_96_0370</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Šerkovice</t>
+          <t>Juliánov (BM)</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Šerkovice</t>
+          <t>Juliánov (BM)</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -41784,34 +41927,34 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0263</t>
+          <t>CLUB_S1994_95_0256</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>Šerkovice = TJ Sokol Šerkovice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Blansko). city Šerkovice.</t>
+          <t>Brno (Juliánov) = TJ Sokol Juliánov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **Juliánov** = mestska cast Brna (Brno-jih). '(BM)' = Brno-mesto. city Brno (Juliánov).</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>Šerkovice</t>
+          <t>Juliánov</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0370</t>
+          <t>CLUB_S1995_96_0371</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Juliánov (BM)</t>
+          <t>Polná</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Juliánov (BM)</t>
+          <t>Polná</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -41826,39 +41969,39 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Brno venkov + Brno město</t>
+          <t>Jihlava</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0256</t>
+          <t>CLUB_S1994_95_0268</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>Brno (Juliánov) = TJ Sokol Juliánov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **Juliánov** = mestska cast Brna (Brno-jih). '(BM)' = Brno-mesto. city Brno (Juliánov).</t>
+          <t>Slavoj Polná. city ✓. || Slavoj Polná 53/54 (30_Jihlavský). DSO reforma. Polná (Wiki D42 - Pavlovo 04/2026). Sokol Polná (49/50-) -&gt; Slavoj Polná (53/54+, DSO reforma) -&gt; kontinuita. city Polná. || Slavoj Polná 53/54 (30_Jihlavský). DSO reforma. Polná (Wiki D42 - Pavlovo 04/2026). Sokol -&gt; Slavoj (53/54+, DSO). city Polná. || Polná = HC Polná (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Jihlava). Hlavni chain: Sokol -&gt; Slavoj Polná -&gt; HC Polná. city Polná.</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>Juliánov</t>
+          <t>Polná</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0371</t>
+          <t>CLUB_S1995_96_0372</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Polná</t>
+          <t>Brtnice</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Polná</t>
+          <t>Brtnice</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -41878,34 +42021,34 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0268</t>
+          <t>CLUB_S1994_95_0271</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>Slavoj Polná. city ✓. || Slavoj Polná 53/54 (30_Jihlavský). DSO reforma. Polná (Wiki D42 - Pavlovo 04/2026). Sokol Polná (49/50-) -&gt; Slavoj Polná (53/54+, DSO reforma) -&gt; kontinuita. city Polná. || Slavoj Polná 53/54 (30_Jihlavský). DSO reforma. Polná (Wiki D42 - Pavlovo 04/2026). Sokol -&gt; Slavoj (53/54+, DSO). city Polná. || Polná = HC Polná (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Jihlava). Hlavni chain: Sokol -&gt; Slavoj Polná -&gt; HC Polná. city Polná.</t>
+          <t>Dlouhá Brtnice = TJ Sokol Dlouhá Brtnice (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Jihlava). city Dlouhá Brtnice.</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>Polná</t>
+          <t>Dlouhá Brtnice</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0372</t>
+          <t>CLUB_S1995_96_0373</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Brtnice</t>
+          <t>Dačice</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Brtnice</t>
+          <t>Dačice</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -41925,34 +42068,34 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0271</t>
+          <t>CLUB_S1994_95_0267</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>Dlouhá Brtnice = TJ Sokol Dlouhá Brtnice (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Jihlava). city Dlouhá Brtnice.</t>
+          <t>Sokol Dačice. city OK. || Dačice = Sokol/HC Dačice (Wiki D42 - registr ustavy 04/2026). Jihocesky/Vysocina kraj (okres Jindřichův Hradec). Mesto kostkoveho cukru. city Dačice.</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>Dlouhá Brtnice</t>
+          <t>Dačice</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0373</t>
+          <t>CLUB_S1995_96_0374</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Dačice</t>
+          <t>Puklice</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Dačice</t>
+          <t>Puklice</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -41972,34 +42115,34 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0267</t>
+          <t>CLUB_S1994_95_0270</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>Sokol Dačice. city OK. || Dačice = Sokol/HC Dačice (Wiki D42 - registr ustavy 04/2026). Jihocesky/Vysocina kraj (okres Jindřichův Hradec). Mesto kostkoveho cukru. city Dačice.</t>
+          <t>Puklice = TJ Sokol Puklice (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Jihlava). city Puklice.</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>Dačice</t>
+          <t>Puklice</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0374</t>
+          <t>CLUB_S1995_96_0375</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Puklice</t>
+          <t>Stonařov</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Puklice</t>
+          <t>Stonařov</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -42017,36 +42160,31 @@
           <t>Jihlava</t>
         </is>
       </c>
-      <c r="H361" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0270</t>
-        </is>
-      </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>Puklice = TJ Sokol Puklice (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Jihlava). city Puklice.</t>
+          <t>Stonařov = TJ Sokol Stonařov (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Jihlava). city Stonařov.</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>Puklice</t>
+          <t>Stonařov</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0375</t>
+          <t>CLUB_S1995_96_0376</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Stonařov</t>
+          <t>Růžená</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Stonařov</t>
+          <t>Růžená</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -42064,31 +42202,36 @@
           <t>Jihlava</t>
         </is>
       </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0269</t>
+        </is>
+      </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>Stonařov = TJ Sokol Stonařov (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Jihlava). city Stonařov.</t>
+          <t>Růžená = TJ Sokol Růžená (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Jihlava). city Růžená.</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>Stonařov</t>
+          <t>Růžená</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0376</t>
+          <t>CLUB_S1995_96_0377</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Růžená</t>
+          <t>Milenov</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Růžená</t>
+          <t>Milenov</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -42103,39 +42246,39 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Jihlava</t>
+          <t>Kroměříž + Přerov</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0269</t>
+          <t>CLUB_S1994_95_0273</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>Růžená = TJ Sokol Růžená (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Jihlava). city Růžená.</t>
+          <t>Milenov = TJ Sokol Milenov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Přerov). city Milenov.</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>Růžená</t>
+          <t>Milenov</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0377</t>
+          <t>CLUB_S1995_96_0378</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Milenov</t>
+          <t>Citov</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Milenov</t>
+          <t>Citov</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -42155,34 +42298,34 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0273</t>
+          <t>CLUB_S1994_95_0276</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>Milenov = TJ Sokol Milenov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Přerov). city Milenov.</t>
+          <t>Citov = TJ Sokol Citov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Přerov). city Citov.</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>Milenov</t>
+          <t>Citov</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0378</t>
+          <t>CLUB_S1995_96_0379</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Citov</t>
+          <t>Zborovice (PŘ)</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Citov</t>
+          <t>Zborovice (PŘ)</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -42202,34 +42345,34 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0276</t>
+          <t>CLUB_S1994_95_0274</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>Citov = TJ Sokol Citov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Přerov). city Citov.</t>
+          <t>Zborovice - almanach bez prefixu (D35, Kroměříž). || Zborovice = TJ Spartak Zborovice (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (okres Kroměříž). Patterns: Sokol -&gt; Spartak Zborovice. city Zborovice.</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>Citov</t>
+          <t>Zborovice</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0379</t>
+          <t>CLUB_S1995_96_0380</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Zborovice (PŘ)</t>
+          <t>Chomýž (PŘ)</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Zborovice (PŘ)</t>
+          <t>Chomýž (PŘ)</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -42249,34 +42392,34 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0274</t>
+          <t>CLUB_S1994_95_0277</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>Zborovice - almanach bez prefixu (D35, Kroměříž). || Zborovice = TJ Spartak Zborovice (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (okres Kroměříž). Patterns: Sokol -&gt; Spartak Zborovice. city Zborovice.</t>
+          <t>Chomýž u Kroměříže = TJ Sokol Chomýž (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (okres Kroměříž, district 'Kroměříž' potvrzen). POZOR: vícero - Chomýž u Krnova (Severomoravsky/Bruntál), Chomýž u Bruntálu. city Chomýž u Kroměříže. || TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0277 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>Zborovice</t>
+          <t>Chomýž</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0380</t>
+          <t>CLUB_S1995_96_0381</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Chomýž (PŘ)</t>
+          <t>Troubky</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Chomýž (PŘ)</t>
+          <t>Troubky</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -42296,34 +42439,34 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0277</t>
+          <t>CLUB_S1994_95_0275</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>Chomýž u Kroměříže = TJ Sokol Chomýž (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (okres Kroměříž, district 'Kroměříž' potvrzen). POZOR: vícero - Chomýž u Krnova (Severomoravsky/Bruntál), Chomýž u Bruntálu. city Chomýž u Kroměříže. || TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0277 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>Sloučení duplicit: kolega měl klub 2× pro různé fáze KS (skupina B + o udržení), automat dal 2 různé cid. Sloučeno: zachovat CLUB_S1954_55_0642, smazat CLUB_S1954_55_0669. || Troubky = Sokol Troubky nL Bečvou (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Přerov). PŘE = Přerov. city Troubky.</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>Chomýž</t>
+          <t>Troubky</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0381</t>
+          <t>CLUB_S1995_96_0382</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Troubky</t>
+          <t>Kojetín</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Troubky</t>
+          <t>Kojetín</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -42343,34 +42486,34 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0275</t>
+          <t>CLUB_S1994_95_0278</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>Sloučení duplicit: kolega měl klub 2× pro různé fáze KS (skupina B + o udržení), automat dal 2 různé cid. Sloučeno: zachovat CLUB_S1954_55_0642, smazat CLUB_S1954_55_0669. || Troubky = Sokol Troubky nL Bečvou (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Přerov). PŘE = Přerov. city Troubky.</t>
+          <t>city ✓ (město u Přerova). || Kojetín = Slavoj Kojetín (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Prerov). city Kojetín.</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>Troubky</t>
+          <t>Kojetín</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0382</t>
+          <t>CLUB_S1995_96_0383</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Kojetín</t>
+          <t>Stařeč</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Kojetín</t>
+          <t>Stařeč</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -42385,39 +42528,39 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Kroměříž + Přerov</t>
+          <t>Třebíč</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0278</t>
+          <t>CLUB_S1994_95_0281</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>city ✓ (město u Přerova). || Kojetín = Slavoj Kojetín (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Prerov). city Kojetín.</t>
+          <t>city ✓ (vesnice u Třebíče). || Stařeč = Sokol Stařeč (Wiki D42 - registr ustavy 04/2026). Vysocina kraj (okres Třebíč). city Stařeč.</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>Kojetín</t>
+          <t>Stařeč</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0383</t>
+          <t>CLUB_S1995_96_0384</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Stařeč</t>
+          <t>Mor.Budějovice</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Stařeč</t>
+          <t>Mor.Budějovice</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -42435,36 +42578,31 @@
           <t>Třebíč</t>
         </is>
       </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0281</t>
-        </is>
-      </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>city ✓ (vesnice u Třebíče). || Stařeč = Sokol Stařeč (Wiki D42 - registr ustavy 04/2026). Vysocina kraj (okres Třebíč). city Stařeč.</t>
+          <t>Moravské Budějovice = TJ Sokol Moravské Budějovice (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Třebíč). PARSING CHYBA: 'Mor.' zkracene. city Moravské Budějovice.</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>Stařeč</t>
+          <t>Mor.Budějovice</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0384</t>
+          <t>CLUB_S1995_96_0385</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Mor.Budějovice</t>
+          <t>Pokojovice</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Mor.Budějovice</t>
+          <t>Pokojovice</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -42482,31 +42620,36 @@
           <t>Třebíč</t>
         </is>
       </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0283</t>
+        </is>
+      </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>Moravské Budějovice = TJ Sokol Moravské Budějovice (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Třebíč). PARSING CHYBA: 'Mor.' zkracene. city Moravské Budějovice.</t>
+          <t>Pokojovice = TJ Sokol Pokojovice (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Třebíč). city Pokojovice.</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>Mor.Budějovice</t>
+          <t>Pokojovice</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0385</t>
+          <t>CLUB_S1995_96_0386</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Pokojovice</t>
+          <t>Studenec</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Pokojovice</t>
+          <t>Studenec</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -42526,34 +42669,34 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0283</t>
+          <t>CLUB_S1994_95_0280</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>Pokojovice = TJ Sokol Pokojovice (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Třebíč). city Pokojovice.</t>
+          <t>Studenec u Velkého Meziříčí = TJ Studenec (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. POZOR: vícero. K overeni. city Studenec u Velkého Meziříčí.</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>Pokojovice</t>
+          <t>Studenec u Vel.Meziříčí</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0386</t>
+          <t>CLUB_S1995_96_0387</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Studenec</t>
+          <t>Okříšky</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Studenec</t>
+          <t>Okříšky</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -42573,34 +42716,34 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0280</t>
+          <t>CLUB_S1994_95_0282</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>Studenec u Velkého Meziříčí = TJ Studenec (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. POZOR: vícero. K overeni. city Studenec u Velkého Meziříčí.</t>
+          <t>B-tým Sokol Okříšky (CLUB_S1952_53_0316). Přejmenováno II → B (D21). prev na 51/52 0333 (A-tým) — žádný B-tým 51/52 neexistoval, B-tým je nový v 52/53. || Okříšky = Sokol Okříšky (Wiki D42 - registr ustavy 04/2026). Jihomoravsky/Vysocina kraj (okres Třebíč). city Okříšky.</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>Studenec u Vel.Meziříčí</t>
+          <t>Okříšky</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0387</t>
+          <t>CLUB_S1995_96_0388</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Okříšky</t>
+          <t>Vladislav</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Okříšky</t>
+          <t>Vladislav</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -42620,34 +42763,34 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0282</t>
+          <t>CLUB_S1994_95_0285</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>B-tým Sokol Okříšky (CLUB_S1952_53_0316). Přejmenováno II → B (D21). prev na 51/52 0333 (A-tým) — žádný B-tým 51/52 neexistoval, B-tým je nový v 52/53. || Okříšky = Sokol Okříšky (Wiki D42 - registr ustavy 04/2026). Jihomoravsky/Vysocina kraj (okres Třebíč). city Okříšky.</t>
+          <t>Vladislav = Sokol/Jiskra Vladislav (Wiki D42 - registr ustavy 04/2026). Vysocina kraj (okres Třebíč). 'Vladislav' jako jmenowy nazev. city Vladislav. || Tasov = Sokol Tasov (Wiki D42 - registr ustavy 04/2026). Vysocina kraj (okres Třebíč nebo Žďár nL Sazavou). city Tasov.</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>Okříšky</t>
+          <t>Vladislav</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0388</t>
+          <t>CLUB_S1995_96_0389</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Vladislav</t>
+          <t>Mohelno</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Vladislav</t>
+          <t>Mohelno</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -42667,34 +42810,34 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0285</t>
+          <t>CLUB_S1994_95_0286</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>Vladislav = Sokol/Jiskra Vladislav (Wiki D42 - registr ustavy 04/2026). Vysocina kraj (okres Třebíč). 'Vladislav' jako jmenowy nazev. city Vladislav. || Tasov = Sokol Tasov (Wiki D42 - registr ustavy 04/2026). Vysocina kraj (okres Třebíč nebo Žďár nL Sazavou). city Tasov.</t>
+          <t>Mohelno = TJ Sokol Mohelno (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Třebíč). **Mohelno** = blizko jaderne elektrarny Dukovany! city Mohelno.</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>Vladislav</t>
+          <t>Mohelno</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0389</t>
+          <t>CLUB_S1995_96_0390</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Mohelno</t>
+          <t>Vyškov B</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Mohelno</t>
+          <t>Vyškov B</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -42709,39 +42852,39 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Třebíč</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0286</t>
+          <t>CLUB_S1994_95_0237</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>Mohelno = TJ Sokol Mohelno (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Třebíč). **Mohelno** = blizko jaderne elektrarny Dukovany! city Mohelno.</t>
+          <t>Vyškov = TJ Vyškov B (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. 'B' = druzstvo B. city Vyškov. || TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0237 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>Mohelno</t>
+          <t>Vyškov B</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0390</t>
+          <t>CLUB_S1995_96_0391</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Vyškov B</t>
+          <t>Velatice</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Vyškov B</t>
+          <t>Velatice</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -42759,36 +42902,31 @@
           <t>Vyškov</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0237</t>
-        </is>
-      </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>Vyškov = TJ Vyškov B (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. 'B' = druzstvo B. city Vyškov. || TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0237 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>Velatice = TJ Sokol Velatice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). city Velatice.</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>Vyškov B</t>
+          <t>Velatice</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0391</t>
+          <t>CLUB_S1995_96_0392</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Velatice</t>
+          <t>Kovalovice</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Velatice</t>
+          <t>Kovalovice</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -42808,29 +42946,29 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>Velatice = TJ Sokol Velatice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). city Velatice.</t>
+          <t>Kovalovice = TJ Sokol Kovalovice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). city Kovalovice.</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>Velatice</t>
+          <t>Kovalovice</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0392</t>
+          <t>CLUB_S1995_96_0393</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Kovalovice</t>
+          <t>Jiříkovice</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Kovalovice</t>
+          <t>Jiříkovice</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -42850,29 +42988,29 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>Kovalovice = TJ Sokol Kovalovice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). city Kovalovice.</t>
+          <t>Jiříkovice = TJ Sokol Jiříkovice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero - Jiříkovice u Brna (Jihomoravsky/Brno-venkov), Jiříkovice u Sumperka. city Jiříkovice.</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>Kovalovice</t>
+          <t>Jiříkovice</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0393</t>
+          <t>CLUB_S1995_96_0394</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Jiříkovice</t>
+          <t>Vítovice</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Jiříkovice</t>
+          <t>Vítovice</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -42890,31 +43028,36 @@
           <t>Vyškov</t>
         </is>
       </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0287</t>
+        </is>
+      </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>Jiříkovice = TJ Sokol Jiříkovice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero - Jiříkovice u Brna (Jihomoravsky/Brno-venkov), Jiříkovice u Sumperka. city Jiříkovice.</t>
+          <t>Vítovice = TJ Sokol Vítovice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Vyškov). 'VYŠ' = Vyškov skupina. POZOR: vícero Vitovic - Vitovice u Vyškova, Vitovice u Brna. city Vítovice.</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>Jiříkovice</t>
+          <t>Vítovice</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0394</t>
+          <t>CLUB_S1995_96_0395</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Vítovice</t>
+          <t>Slavkov</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Vítovice</t>
+          <t>Slavkov</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -42934,34 +43077,34 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0287</t>
+          <t>CLUB_S1994_95_0302</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>Vítovice = TJ Sokol Vítovice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Vyškov). 'VYŠ' = Vyškov skupina. POZOR: vícero Vitovic - Vitovice u Vyškova, Vitovice u Brna. city Vítovice.</t>
+          <t>Slavkovice = TJ Sokol Slavkovice (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Žďár nL Sázavou). city Slavkovice.</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>Vítovice</t>
+          <t>Slavkovice</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0395</t>
+          <t>CLUB_S1995_96_0396</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Slavkov</t>
+          <t>Nížkovice</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Slavkov</t>
+          <t>Nížkovice</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -42979,36 +43122,31 @@
           <t>Vyškov</t>
         </is>
       </c>
-      <c r="H382" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0302</t>
-        </is>
-      </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>Slavkovice = TJ Sokol Slavkovice (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Žďár nL Sázavou). city Slavkovice.</t>
+          <t>Nížkovice = TJ Sokol Nížkovice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Vyškov). city Nížkovice.</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>Slavkovice</t>
+          <t>Nížkovice</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0396</t>
+          <t>CLUB_S1995_96_0397</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Nížkovice</t>
+          <t>Želechovice</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Nížkovice</t>
+          <t>Želechovice</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -43023,34 +43161,39 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Zlín + Uh.Hradiště</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0288</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>Nížkovice = TJ Sokol Nížkovice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Vyškov). city Nížkovice.</t>
+          <t>Želechovice = TJ Želechovice (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (mestska cast Zlina - Zelechovice nL Drevnici). city Želechovice.</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>Nížkovice</t>
+          <t>Želechovice</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0397</t>
+          <t>CLUB_S1995_96_0398</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Želechovice</t>
+          <t>Technika Zlín</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Želechovice</t>
+          <t>Technika Zlín</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -43070,34 +43213,34 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0288</t>
+          <t>CLUB_S1994_95_0290</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>Želechovice = TJ Želechovice (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (mestska cast Zlina - Zelechovice nL Drevnici). city Želechovice.</t>
+          <t>Zlín = TJ Technika Zlín (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Technika** = vysokoskolsky klub (VUT Zlín / UTB). city Zlín.</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>Želechovice</t>
+          <t>Technika Zlín</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0398</t>
+          <t>CLUB_S1995_96_0399</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Technika Zlín</t>
+          <t>Z.club Zlín</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Technika Zlín</t>
+          <t>Z.club Zlín</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -43115,36 +43258,31 @@
           <t>Zlín + Uh.Hradiště</t>
         </is>
       </c>
-      <c r="H385" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0290</t>
-        </is>
-      </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>Zlín = TJ Technika Zlín (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Technika** = vysokoskolsky klub (VUT Zlín / UTB). city Zlín.</t>
+          <t>Zlín = TJ Z-club Zlín (Wiki D42 - registr ustavy 04/2026). Zlinsky kraj. Patterns: Z-klub Zlín. city Zlín.</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>Technika Zlín</t>
+          <t>Z.club Zlín</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0399</t>
+          <t>CLUB_S1995_96_0400</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Z.club Zlín</t>
+          <t>Uh. Ostroh B (UH)</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Z.club Zlín</t>
+          <t>Uh. Ostroh B (UH)</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -43164,29 +43302,29 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>Zlín = TJ Z-club Zlín (Wiki D42 - registr ustavy 04/2026). Zlinsky kraj. Patterns: Z-klub Zlín. city Zlín.</t>
+          <t>Uherský Ostroh = HC Uherský Ostroh B (Wiki D42 - registr ustavy 04/2026). Zlinsky kraj (okres Uherské Hradiště). 'B' = druzstvo B, '(UH)' = okres Uherské Hradiště. city Uherský Ostroh.</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>Z.club Zlín</t>
+          <t>Uh. Ostroh B</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0400</t>
+          <t>CLUB_S1995_96_0401</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Uh. Ostroh B (UH)</t>
+          <t>Bojkovice (UH)</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Uh. Ostroh B (UH)</t>
+          <t>Bojkovice (UH)</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -43204,31 +43342,36 @@
           <t>Zlín + Uh.Hradiště</t>
         </is>
       </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0292</t>
+        </is>
+      </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>Uherský Ostroh = HC Uherský Ostroh B (Wiki D42 - registr ustavy 04/2026). Zlinsky kraj (okres Uherské Hradiště). 'B' = druzstvo B, '(UH)' = okres Uherské Hradiště. city Uherský Ostroh.</t>
+          <t>Bojkovice = TJ Bojkovice (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (okres Uherske Hradiste). city Bojkovice.</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>Uh. Ostroh B</t>
+          <t>Bojkovice</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0401</t>
+          <t>CLUB_S1995_96_0402</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Bojkovice (UH)</t>
+          <t>Orli Znojmo B</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Bojkovice (UH)</t>
+          <t>Orli Znojmo B</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -43243,39 +43386,39 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Zlín + Uh.Hradiště</t>
+          <t>Znojmo</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0292</t>
+          <t>CLUB_S1994_95_0293</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>Bojkovice = TJ Bojkovice (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (okres Uherske Hradiste). city Bojkovice.</t>
+          <t>Znojmo = HC Znojmo B (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. 'B' = druzstvo B. city Znojmo.</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>Bojkovice</t>
+          <t>Znojmo B</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0402</t>
+          <t>CLUB_S1995_96_0403</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Orli Znojmo B</t>
+          <t>Remix Znojmo</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Orli Znojmo B</t>
+          <t>Remix Znojmo</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -43293,36 +43436,31 @@
           <t>Znojmo</t>
         </is>
       </c>
-      <c r="H389" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0293</t>
-        </is>
-      </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>Znojmo = HC Znojmo B (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. 'B' = druzstvo B. city Znojmo.</t>
+          <t>Znojmo = HC Remix Znojmo (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Post-revolucni sponzor. city Znojmo.</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>Znojmo B</t>
+          <t>Remix Znojmo</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0403</t>
+          <t>CLUB_S1995_96_0404</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Remix Znojmo</t>
+          <t>Horní Dunajovice</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Remix Znojmo</t>
+          <t>Horní Dunajovice</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -43340,31 +43478,36 @@
           <t>Znojmo</t>
         </is>
       </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0297</t>
+        </is>
+      </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>Znojmo = HC Remix Znojmo (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Post-revolucni sponzor. city Znojmo.</t>
+          <t>Horní Dunajovice = TJ Družstevník Horní Dunajovice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). city Horní Dunajovice.</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>Remix Znojmo</t>
+          <t>Družstevník Horní Dunajovice</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0404</t>
+          <t>CLUB_S1995_96_0405</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Horní Dunajovice</t>
+          <t>JAPA Žďár nad Sázavou</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Horní Dunajovice</t>
+          <t>JAPA Žďár nad Sázavou</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -43379,39 +43522,39 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Znojmo</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0297</t>
+          <t>CLUB_S1994_95_0070</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>Horní Dunajovice = TJ Družstevník Horní Dunajovice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). city Horní Dunajovice.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>Družstevník Horní Dunajovice</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0405</t>
+          <t>CLUB_S1995_96_0406</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>JAPA Žďár nad Sázavou</t>
+          <t>Granit Žďár nad Sázavou</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>JAPA Žďár nad Sázavou</t>
+          <t>Granit Žďár nad Sázavou</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -43448,17 +43591,17 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0406</t>
+          <t>CLUB_S1995_96_0407</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Granit Žďár nad Sázavou</t>
+          <t>Velké Meziříčí B</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Granit Žďár nad Sázavou</t>
+          <t>Velké Meziříčí B</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -43478,34 +43621,34 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0070</t>
+          <t>CLUB_S1994_95_0305</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>Sokol Velké Meziříčí. Jiný klub od 0484 (CLUB_S1954_55_0484 bez prefixu). || Sokol Velké Meziříčí 54/55 (30_Jihlavský). Velké Meziříčí = HHK Velké Meziříčí (Wiki D42 - Pavlovo 04/2026). Velké Meziříčí (50/51-) -&gt; Sokol Velké Meziříčí (54/55) -&gt; Spartak Velké Meziříčí (56/57+, DSO reforma) -&gt; kontinuita -&gt; HHK Velké Meziříčí. Patterns: Velké Meziříčí, Sokol VM, Spartak VM. POZOR: 50/51 0731 'České Meziříčí' je JINE MESTO (Královéhradecký). Tatran Valašské Meziříčí je tez JINE MESTO (Gottwaldovský/Zlinsky). city Velké Meziříčí. || Sokol Velké Meziříčí 54/55 (30_Jihlavský). Velké Meziříčí = HHK VM (Wiki D42 - Pavlovo 04/2026). Sokol VM -&gt; Spartak VM (56/57+). NE České ani Valašské Meziříčí. city Velké Meziříčí. || Velké Meziříčí = Spartak/HC Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. POZOR: NE Valašské Meziříčí (Severomoravsky/Zlinsky)! city Velké Meziříčí.</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>Žďár nad Sázavou</t>
+          <t>Velké Meziříčí</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0407</t>
+          <t>CLUB_S1995_96_0408</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Velké Meziříčí B</t>
+          <t>Měřín</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Velké Meziříčí B</t>
+          <t>Měřín</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -43525,34 +43668,34 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0305</t>
+          <t>CLUB_S1994_95_0303</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>Sokol Velké Meziříčí. Jiný klub od 0484 (CLUB_S1954_55_0484 bez prefixu). || Sokol Velké Meziříčí 54/55 (30_Jihlavský). Velké Meziříčí = HHK Velké Meziříčí (Wiki D42 - Pavlovo 04/2026). Velké Meziříčí (50/51-) -&gt; Sokol Velké Meziříčí (54/55) -&gt; Spartak Velké Meziříčí (56/57+, DSO reforma) -&gt; kontinuita -&gt; HHK Velké Meziříčí. Patterns: Velké Meziříčí, Sokol VM, Spartak VM. POZOR: 50/51 0731 'České Meziříčí' je JINE MESTO (Královéhradecký). Tatran Valašské Meziříčí je tez JINE MESTO (Gottwaldovský/Zlinsky). city Velké Meziříčí. || Sokol Velké Meziříčí 54/55 (30_Jihlavský). Velké Meziříčí = HHK VM (Wiki D42 - Pavlovo 04/2026). Sokol VM -&gt; Spartak VM (56/57+). NE České ani Valašské Meziříčí. city Velké Meziříčí. || Velké Meziříčí = Spartak/HC Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. POZOR: NE Valašské Meziříčí (Severomoravsky/Zlinsky)! city Velké Meziříčí.</t>
+          <t>Měřín = TJ Měřín (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Žďár nL Sázavou). city Měřín.</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>Velké Meziříčí</t>
+          <t>Měřín</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0408</t>
+          <t>CLUB_S1995_96_0409</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Měřín</t>
+          <t>Slavkovice</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Měřín</t>
+          <t>Slavkovice</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -43572,34 +43715,34 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0303</t>
+          <t>CLUB_S1994_95_0302</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>Měřín = TJ Měřín (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Žďár nL Sázavou). city Měřín.</t>
+          <t>Slavkovice = TJ Sokol Slavkovice (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Žďár nL Sázavou). city Slavkovice.</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>Měřín</t>
+          <t>Slavkovice</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0409</t>
+          <t>CLUB_S1995_96_0410</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Slavkovice</t>
+          <t>Křižanov</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Slavkovice</t>
+          <t>Křižanov</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -43619,34 +43762,34 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0302</t>
+          <t>CLUB_S1994_95_0304</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>Slavkovice = TJ Sokol Slavkovice (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Žďár nL Sázavou). city Slavkovice.</t>
+          <t>Křižanov = TJ Sokol Křižanov (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Žďár nL Sázavou). NE Křižanovice u Bučovic (Jihomoravsky)! Birthplace **sv. Zdislavy z Lemberka** (13. st.). city Křižanov.</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>Slavkovice</t>
+          <t>Křižanov</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0410</t>
+          <t>CLUB_S1995_96_0411</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Křižanov</t>
+          <t>Vojnův Městec</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Křižanov</t>
+          <t>Vojnův Městec</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -43666,34 +43809,34 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0304</t>
+          <t>CLUB_S1994_95_0301</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>Křižanov = TJ Sokol Křižanov (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Žďár nL Sázavou). NE Křižanovice u Bučovic (Jihomoravsky)! Birthplace **sv. Zdislavy z Lemberka** (13. st.). city Křižanov.</t>
+          <t>Vojnův Městec = TJ Vojnův Městec (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Žďár nL Sázavou). city Vojnův Městec.</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>Křižanov</t>
+          <t>Vojnův Městec</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0411</t>
+          <t>CLUB_S1995_96_0412</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Vojnův Městec</t>
+          <t>Netín</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Vojnův Městec</t>
+          <t>Netín</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -43711,78 +43854,73 @@
           <t>Žďár nad Sázavou</t>
         </is>
       </c>
-      <c r="H398" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0301</t>
-        </is>
-      </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>Vojnův Městec = TJ Vojnův Městec (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Žďár nL Sázavou). city Vojnův Městec.</t>
+          <t>Netín = TJ Sokol Netín (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Žďár nL Sázavou). city Netín.</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>Vojnův Městec</t>
+          <t>Netín</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0412</t>
+          <t>CLUB_S1995_96_0414</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Netín</t>
+          <t>HC Poruba</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Netín</t>
+          <t>HC Poruba</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>30_Jihomoravský</t>
+          <t>30_Severomoravský</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>okresní</t>
-        </is>
-      </c>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>Žďár nad Sázavou</t>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0311</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>Netín = TJ Sokol Netín (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Žďár nL Sázavou). city Netín.</t>
+          <t>Baník Ostrava B (B-tým Baníku Ostrava). Level → L25 (KVAL). clean: "II" → "B" (D21). city: "OKD Ostrava" → "Ostrava". prev=54/55 0008 (Baník Ostrava, A-tým, který v 54/55 byl v 1. lize, v 55/56 sestoupil do 2. ligy jako 0017). POZOR: Baník Ostrava ≠ Baník Vítkovice (samostatný klub). || Ostrava = HC Vitkovice Steel + HC Banik Ostrava (Wiki D42 - registr ustavy 04/2026). Vice paralelnich chains v Ostrave (krajska metropole). HLAVNI: (1) HC Vítkovice = ZSJ VŽKG (1949+, VŽKG = Vitkovice Železarny K. Gottwalda) -&gt; Spartak VŽKG -&gt; Vítkovice -&gt; HC Vítkovice Steel. (2) HC Banik Ostrava: NHKG (Nova hut K. Gottwalda) -&gt; Banik NHKG -&gt; Banik Ostrava -&gt; 1995 prestehovani do Karviny. (3) Slavia VŠB Ostrava (akademicky), Slovan Hrabuvka. ČSSZ Kuncice = Československé stavební závody. city Ostrava. || TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0311 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>Netín</t>
+          <t>Ostrava</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0414</t>
+          <t>CLUB_S1995_96_0415</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>HC Poruba</t>
+          <t>Kopřivnice</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>HC Poruba</t>
+          <t>Kopřivnice</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -43797,34 +43935,34 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0311</t>
+          <t>CLUB_S1994_95_0308</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>Baník Ostrava B (B-tým Baníku Ostrava). Level → L25 (KVAL). clean: "II" → "B" (D21). city: "OKD Ostrava" → "Ostrava". prev=54/55 0008 (Baník Ostrava, A-tým, který v 54/55 byl v 1. lize, v 55/56 sestoupil do 2. ligy jako 0017). POZOR: Baník Ostrava ≠ Baník Vítkovice (samostatný klub). || Ostrava = HC Vitkovice Steel + HC Banik Ostrava (Wiki D42 - registr ustavy 04/2026). Vice paralelnich chains v Ostrave (krajska metropole). HLAVNI: (1) HC Vítkovice = ZSJ VŽKG (1949+, VŽKG = Vitkovice Železarny K. Gottwalda) -&gt; Spartak VŽKG -&gt; Vítkovice -&gt; HC Vítkovice Steel. (2) HC Banik Ostrava: NHKG (Nova hut K. Gottwalda) -&gt; Banik NHKG -&gt; Banik Ostrava -&gt; 1995 prestehovani do Karviny. (3) Slavia VŠB Ostrava (akademicky), Slovan Hrabuvka. ČSSZ Kuncice = Československé stavební závody. city Ostrava. || TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0311 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>Kopřivnice = HC ISMM Kopřivnice (Wiki - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Mestske TATRA - automobilka. Patterns: Tatra Koprivnice, ISMM. city Kopřivnice.</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>Ostrava</t>
+          <t>Tatra Kopřivnice</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0415</t>
+          <t>CLUB_S1995_96_0416</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Kopřivnice</t>
+          <t>Valašské Meziříčí</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Kopřivnice</t>
+          <t>Valašské Meziříčí (N)</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -43832,6 +43970,11 @@
           <t>30_Severomoravský</t>
         </is>
       </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F401" t="inlineStr">
         <is>
           <t>L40</t>
@@ -43839,34 +43982,34 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0308</t>
+          <t>CLUB_S1994_95_0313</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>Kopřivnice = HC ISMM Kopřivnice (Wiki - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Mestske TATRA - automobilka. Patterns: Tatra Koprivnice, ISMM. city Kopřivnice.</t>
+          <t>Odstranění suffixu „A" (kolegova nedůslednost). Rozšíření „Val.Meziříčí" → „Valašské Meziříčí" (plný název v clean i city). || PS Valašské Meziříčí 52/53. PS = Poz.stavby? Valašské Meziříčí = JINÉ MĚSTO od Velké Meziříčí! Valašské Meziříčí = mesto v Zlinsky kraji (Gottwaldovský/Zlinsky), Vsetinsky/Roznovsky region. Tatran Val.Meziříčí, PS, Tesla Val.Meziříčí. Wiki D42 - Pavlovo 04/2026. city Valašské Meziříčí. || PS Valašské Meziříčí 52/53. PS = Poz.stavby. Valašské Meziříčí = JINÉ MĚSTO od Velké Meziříčí! Mesto v Zlinsky kraji, Vsetinsky region. Wiki D42 - Pavlovo 04/2026. city Valašské Meziříčí. || Valašské Meziříčí = HC Bobři Valašské Meziříčí (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Zlinsky kraj. Tesla Valašské Meziříčí (podnik) -&gt; PS Valašské Meziříčí (Pozemni stavby) -&gt; TJ -&gt; Bobri. POZOR: NE Velke Mezirici (Vysocina). city Valašské Meziříčí.</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>Tatra Kopřivnice</t>
+          <t>Valašské Meziříčí</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0416</t>
+          <t>CLUB_S1995_96_0417</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Valašské Meziříčí</t>
+          <t>HC Třinec</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Valašské Meziříčí (N)</t>
+          <t>HC Třinec (N)</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -43886,34 +44029,34 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0313</t>
+          <t>CLUB_S1994_95_0314</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>Odstranění suffixu „A" (kolegova nedůslednost). Rozšíření „Val.Meziříčí" → „Valašské Meziříčí" (plný název v clean i city). || PS Valašské Meziříčí 52/53. PS = Poz.stavby? Valašské Meziříčí = JINÉ MĚSTO od Velké Meziříčí! Valašské Meziříčí = mesto v Zlinsky kraji (Gottwaldovský/Zlinsky), Vsetinsky/Roznovsky region. Tatran Val.Meziříčí, PS, Tesla Val.Meziříčí. Wiki D42 - Pavlovo 04/2026. city Valašské Meziříčí. || PS Valašské Meziříčí 52/53. PS = Poz.stavby. Valašské Meziříčí = JINÉ MĚSTO od Velké Meziříčí! Mesto v Zlinsky kraji, Vsetinsky region. Wiki D42 - Pavlovo 04/2026. city Valašské Meziříčí. || Valašské Meziříčí = HC Bobři Valašské Meziříčí (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Zlinsky kraj. Tesla Valašské Meziříčí (podnik) -&gt; PS Valašské Meziříčí (Pozemni stavby) -&gt; TJ -&gt; Bobri. POZOR: NE Velke Mezirici (Vysocina). city Valašské Meziříčí.</t>
+          <t>A-tým Baník Třinec. Smart fix prev: chybělo → 52/53 0475 (Sokol Železárny VMM Třinec). Identity transition Sokol Železárny VMM → Baník (D28) + zkrácení názvu. || Baník Třinec 53/54 (30_Ostravský). KLÍČOVÝ ROK přejmenování - DSO Baník 1953. Třinec = HC Oceláři Třinec (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Třinec (1929) -&gt; KS Zaolzie (1938-39, Klub Sportowy Zaolzie - polske obdobi po Mnichove, Zaolzie = ceske uzemi za Olzou) -&gt; SK Železárny Třinec (1939) -&gt; TJ TŽ VŘSR Třinec (1950, VŘSR = Velke rijnove socialisticke revoluce, TŽ = Třinecké železárny) -&gt; TJ TŽ Třinec (1988, vypustil VŘSR) -&gt; HC Železárny Třinec (1994) -&gt; HC Oceláři Třinec (1999-dnes). POZN: Almanach 50/51 'Železárny Molotova Třinec' = TJ TŽ Molotov / VMM = patron Vjaceslav Molotov (nikoli VŘSR jak Wiki) - pravdepodobne kolega zaznamenal jinou variantu nazvu. Patterns: Železárny Molotova Třinec, Sokol Železárny VMM Třinec, Baník Třinec, TŽ Třinec. city Třinec. || Třinec = HC Oceláři Třinec (Wiki D42 - registr ustavy 04/2026). Vsechny trinecke kluby. Hlavni chain: TŽ (Třinecké železárny) Třinec -&gt; Banik Třinec -&gt; Sokol -&gt; Spartak -&gt; Banik -&gt; ZSJ TŽ -&gt; HC Oceláři Třinec. OUPZ Třinec III = paralelni. city Třinec.</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>Valašské Meziříčí</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0417</t>
+          <t>CLUB_S1995_96_0418</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>HC Třinec</t>
+          <t>Uničov</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>HC Třinec (N)</t>
+          <t>Uničov</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -43921,11 +44064,6 @@
           <t>30_Severomoravský</t>
         </is>
       </c>
-      <c r="E403" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F403" t="inlineStr">
         <is>
           <t>L40</t>
@@ -43933,34 +44071,34 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0314</t>
+          <t>CLUB_S1994_95_0310</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>A-tým Baník Třinec. Smart fix prev: chybělo → 52/53 0475 (Sokol Železárny VMM Třinec). Identity transition Sokol Železárny VMM → Baník (D28) + zkrácení názvu. || Baník Třinec 53/54 (30_Ostravský). KLÍČOVÝ ROK přejmenování - DSO Baník 1953. Třinec = HC Oceláři Třinec (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Třinec (1929) -&gt; KS Zaolzie (1938-39, Klub Sportowy Zaolzie - polske obdobi po Mnichove, Zaolzie = ceske uzemi za Olzou) -&gt; SK Železárny Třinec (1939) -&gt; TJ TŽ VŘSR Třinec (1950, VŘSR = Velke rijnove socialisticke revoluce, TŽ = Třinecké železárny) -&gt; TJ TŽ Třinec (1988, vypustil VŘSR) -&gt; HC Železárny Třinec (1994) -&gt; HC Oceláři Třinec (1999-dnes). POZN: Almanach 50/51 'Železárny Molotova Třinec' = TJ TŽ Molotov / VMM = patron Vjaceslav Molotov (nikoli VŘSR jak Wiki) - pravdepodobne kolega zaznamenal jinou variantu nazvu. Patterns: Železárny Molotova Třinec, Sokol Železárny VMM Třinec, Baník Třinec, TŽ Třinec. city Třinec. || Třinec = HC Oceláři Třinec (Wiki D42 - registr ustavy 04/2026). Vsechny trinecke kluby. Hlavni chain: TŽ (Třinecké železárny) Třinec -&gt; Banik Třinec -&gt; Sokol -&gt; Spartak -&gt; Banik -&gt; ZSJ TŽ -&gt; HC Oceláři Třinec. OUPZ Třinec III = paralelni. city Třinec.</t>
+          <t>Uničov = TJ Spartak Uničov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Olomouc). city Uničov.</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Uničov</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0418</t>
+          <t>CLUB_S1995_96_0419</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Uničov</t>
+          <t>Studénka</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Uničov</t>
+          <t>Studénka</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -43975,34 +44113,34 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0310</t>
+          <t>CLUB_S1994_95_0312</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>Uničov = TJ Spartak Uničov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Olomouc). city Uničov.</t>
+          <t>Studénka = TJ Tatra Vagónka Studénka (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). **Vagónka Studénka** = vyrobce železničních vagónů (Tatra Studénka pobocka). city Studénka.</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>Uničov</t>
+          <t>Vagónka Studénka</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0419</t>
+          <t>CLUB_S1995_96_0420</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Studénka</t>
+          <t>Stará Bělá</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Studénka</t>
+          <t>Stará Bělá</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -44017,34 +44155,34 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0312</t>
+          <t>CLUB_S1994_95_0319</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>Studénka = TJ Tatra Vagónka Studénka (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). **Vagónka Studénka** = vyrobce železničních vagónů (Tatra Studénka pobocka). city Studénka.</t>
+          <t>Sokol Stará Bělá (district=Přebor). city ✓. || Stará Bělá = Sokol/Spartak Stará Bělá (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (mestska cast Ostravy). city Stará Bělá.</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>Vagónka Studénka</t>
+          <t>Stará Bělá</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0420</t>
+          <t>CLUB_S1995_96_0421</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Stará Bělá</t>
+          <t>Bohumín</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Stará Bělá</t>
+          <t>Bohumín (N)</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -44052,41 +44190,41 @@
           <t>30_Severomoravský</t>
         </is>
       </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F406" t="inlineStr">
         <is>
           <t>L40</t>
         </is>
       </c>
-      <c r="H406" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0319</t>
-        </is>
-      </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>Sokol Stará Bělá (district=Přebor). city ✓. || Stará Bělá = Sokol/Spartak Stará Bělá (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (mestska cast Ostravy). city Stará Bělá.</t>
+          <t>Baník Bohumín BŽKG (BŽKG = Bohumínské železárny K. Gottwalda, závod). Oprava city: "Bohumín BŽKG" → "Bohumín". || Bohumín = TJ Banik BŽKG Bohumín / TJ Banik ŽD Bohumín (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **BŽKG** = Bohumínské železárny K. Gottwalda (NE VŽKG = Vítkovické železárny K. Gottwalda!). **ŽD** = Železárny Dolu / Železárny Dolní Bohumín. Patterns: Sokol Bohumin -&gt; Banik BŽKG Bohumín -&gt; Banik ŽD Bohumín. city Bohumín.</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>Stará Bělá</t>
+          <t>Bohumín</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0421</t>
+          <t>CLUB_S1995_96_0422</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Bohumín</t>
+          <t>Rožnov pod Radhoštěm</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Bohumín (N)</t>
+          <t>Rožnov pod Radhoštěm</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -44094,41 +44232,41 @@
           <t>30_Severomoravský</t>
         </is>
       </c>
-      <c r="E407" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F407" t="inlineStr">
         <is>
           <t>L40</t>
         </is>
       </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0317</t>
+        </is>
+      </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>Baník Bohumín BŽKG (BŽKG = Bohumínské železárny K. Gottwalda, závod). Oprava city: "Bohumín BŽKG" → "Bohumín". || Bohumín = TJ Banik BŽKG Bohumín / TJ Banik ŽD Bohumín (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **BŽKG** = Bohumínské železárny K. Gottwalda (NE VŽKG = Vítkovické železárny K. Gottwalda!). **ŽD** = Železárny Dolu / Železárny Dolní Bohumín. Patterns: Sokol Bohumin -&gt; Banik BŽKG Bohumín -&gt; Banik ŽD Bohumín. city Bohumín.</t>
+          <t>Rožnov pod Radhoštěm = TJ Rožnov pod Radhoštěm (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (okres Vsetin), Beskydy. **Tesla Rožnov** = elektrotechnicky podnik. city Rožnov pod Radhoštěm.</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>Bohumín</t>
+          <t>Rožnov pod Radhoštěm</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0422</t>
+          <t>CLUB_S1995_96_0423</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Rožnov pod Radhoštěm</t>
+          <t>Frýdek Místek B</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Rožnov pod Radhoštěm</t>
+          <t>Frýdek Místek B (N)</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -44136,6 +44274,11 @@
           <t>30_Severomoravský</t>
         </is>
       </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F408" t="inlineStr">
         <is>
           <t>L40</t>
@@ -44143,34 +44286,34 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0317</t>
+          <t>CLUB_S1994_95_0063</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>Rožnov pod Radhoštěm = TJ Rožnov pod Radhoštěm (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (okres Vsetin), Beskydy. **Tesla Rožnov** = elektrotechnicky podnik. city Rožnov pod Radhoštěm.</t>
+          <t>Frýdek-Místek = HC Frýdek-Místek B (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. 'B' = druzstvo B. city Frýdek-Místek. || TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>Rožnov pod Radhoštěm</t>
+          <t>Frýdek Místek B</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0423</t>
+          <t>CLUB_S1995_96_0424</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Frýdek Místek B</t>
+          <t>Frenštát pod Radhoštěm</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Frýdek Místek B (N)</t>
+          <t>Frenštát pod Radhoštěm</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -44178,11 +44321,6 @@
           <t>30_Severomoravský</t>
         </is>
       </c>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F409" t="inlineStr">
         <is>
           <t>L40</t>
@@ -44190,34 +44328,34 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0063</t>
+          <t>CLUB_S1994_95_0316</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>Frýdek-Místek = HC Frýdek-Místek B (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. 'B' = druzstvo B. city Frýdek-Místek. || TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>Spartak Frenštát pod Radhoštěm (Nový Jičín). Oprava clean+city: "Frenštát" → "Frenštát pod Radhoštěm" (plný název). || Frenštát pL Radhoštěm = Spartak/MEZ Frenštát (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). MEZ = Moravske elektrotechnicke zavody (Vsetin pobocka). city Frenštát pod Radhoštěm.</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>Frýdek Místek B</t>
+          <t>Frenštát pod Radhoštěm</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0424</t>
+          <t>CLUB_S1995_96_0425</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Frenštát pod Radhoštěm</t>
+          <t>ČSAD Ostrava</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Frenštát pod Radhoštěm</t>
+          <t>ČSAD Ostrava (N)</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -44225,41 +44363,41 @@
           <t>30_Severomoravský</t>
         </is>
       </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F410" t="inlineStr">
         <is>
           <t>L40</t>
         </is>
       </c>
-      <c r="H410" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0316</t>
-        </is>
-      </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>Spartak Frenštát pod Radhoštěm (Nový Jičín). Oprava clean+city: "Frenštát" → "Frenštát pod Radhoštěm" (plný název). || Frenštát pL Radhoštěm = Spartak/MEZ Frenštát (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). MEZ = Moravske elektrotechnicke zavody (Vsetin pobocka). city Frenštát pod Radhoštěm.</t>
+          <t>Ostrava = TJ ČSAD Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. ČSAD. city Ostrava.</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>Frenštát pod Radhoštěm</t>
+          <t>ČSAD Ostrava</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0425</t>
+          <t>CLUB_S1995_96_0426</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>ČSAD Ostrava</t>
+          <t>Svinov</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>ČSAD Ostrava (N)</t>
+          <t>Svinov</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -44267,41 +44405,41 @@
           <t>30_Severomoravský</t>
         </is>
       </c>
-      <c r="E411" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F411" t="inlineStr">
         <is>
           <t>L40</t>
         </is>
       </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0315</t>
+        </is>
+      </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>Ostrava = TJ ČSAD Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. ČSAD. city Ostrava.</t>
+          <t>Sloučení duplicit: kolega zaregistroval „Baník Svinov" 2× pro různé fáze KS B (skupina B + finále/o udržení), automat dal různé cid. Zachovat CLUB_S1955_56_0778, smazat CLUB_S1955_56_0802 (D39 KP fáze, 1 cid). || Svinov = TJ Banik Svinov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (mestska cast Ostravy). NE Svinov u Sumperka. Patterns: Sokol Svinov -&gt; Banik Svinov. city Svinov.</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>ČSAD Ostrava</t>
+          <t>Svinov</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0426</t>
+          <t>CLUB_S1995_96_0427</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Svinov</t>
+          <t>Kozlovice</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Svinov</t>
+          <t>Kozlovice (N)</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -44309,41 +44447,41 @@
           <t>30_Severomoravský</t>
         </is>
       </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F412" t="inlineStr">
         <is>
           <t>L40</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0315</t>
-        </is>
-      </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>Sloučení duplicit: kolega zaregistroval „Baník Svinov" 2× pro různé fáze KS B (skupina B + finále/o udržení), automat dal různé cid. Zachovat CLUB_S1955_56_0778, smazat CLUB_S1955_56_0802 (D39 KP fáze, 1 cid). || Svinov = TJ Banik Svinov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (mestska cast Ostravy). NE Svinov u Sumperka. Patterns: Sokol Svinov -&gt; Banik Svinov. city Svinov.</t>
+          <t>Kozlovice = TJ Sokol Kozlovice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero - Kozlovice u Frýdku-Místku (Severomoravsko), Kozlovice u Olomouce. K overeni. city Kozlovice.</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>Svinov</t>
+          <t>Kozlovice</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0427</t>
+          <t>CLUB_S1995_96_0428</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Kozlovice</t>
+          <t>Krnov B</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Kozlovice (N)</t>
+          <t>Krnov B</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -44351,41 +44489,41 @@
           <t>30_Severomoravský</t>
         </is>
       </c>
-      <c r="E413" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F413" t="inlineStr">
         <is>
           <t>L40</t>
         </is>
       </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0322</t>
+        </is>
+      </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>Kozlovice = TJ Sokol Kozlovice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero - Kozlovice u Frýdku-Místku (Severomoravsko), Kozlovice u Olomouce. K overeni. city Kozlovice.</t>
+          <t>Krnov = TJ Krnov B (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. 'B' = druzstvo B. city Krnov. || TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0322 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>Kozlovice</t>
+          <t>Krnov B</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0428</t>
+          <t>CLUB_S1995_96_0429</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Krnov B</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Krnov B</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -44400,34 +44538,34 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0322</t>
+          <t>CLUB_S1994_95_0320</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>Krnov = TJ Krnov B (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. 'B' = druzstvo B. city Krnov. || TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0322 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>Brano Horní Benešov 52/53 (20_Ostravský). Brano = strojirensky podnik. Horní Benešov + Dolní Benešov = JINE MESTO od Benesov u Prahy (Stredocesky)! Horní Benešov / Dolní Benešov jsou obce ve Slezsku (Bruntal/Opava) - Ostravsky kraj. Brano Horní Benešov = strojirensky podnik Brano. MSA Dolní Benešov = MSA strojirenstvi. Wiki D42 - Pavlovo upresneni 04/2026. NE Benesov u Prahy chain! || Brano Horní Benešov 52/53 (20_Ostravský). Brano = Brany podnik. Horní Benešov / Dolní Benešov = JINÉ MĚSTO od Benešov (Stredocesky). Horní Benešov = mesto v okrese Bruntal (Olomoucky/Moravskoslezsky). Dolní Benešov = mesto v okrese Opava (Moravskoslezsky). Brano = Brany podnik (Horni Benesov, vyroba dveri). MSA = Moravskoslezska armaturka (Dolni Benesov). Wiki D42 - Pavlovo upresneni 04/2026. city Horní Benešov / Dolní Benešov (NIKDY neni Stredocesky Benesov). || Horní Benešov = Spartak Horní Benešov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntal). POZOR: Dolni Benesov u Opavy! Vsichni Benešovi v okrese - Horni, Dolni, Benesov u Prahy. city Horní Benešov.</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>Krnov B</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0429</t>
+          <t>CLUB_S1995_96_0430</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>B.D. Opava</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>B.D. Opava</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -44440,36 +44578,31 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H415" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0320</t>
-        </is>
-      </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>Brano Horní Benešov 52/53 (20_Ostravský). Brano = strojirensky podnik. Horní Benešov + Dolní Benešov = JINE MESTO od Benesov u Prahy (Stredocesky)! Horní Benešov / Dolní Benešov jsou obce ve Slezsku (Bruntal/Opava) - Ostravsky kraj. Brano Horní Benešov = strojirensky podnik Brano. MSA Dolní Benešov = MSA strojirenstvi. Wiki D42 - Pavlovo upresneni 04/2026. NE Benesov u Prahy chain! || Brano Horní Benešov 52/53 (20_Ostravský). Brano = Brany podnik. Horní Benešov / Dolní Benešov = JINÉ MĚSTO od Benešov (Stredocesky). Horní Benešov = mesto v okrese Bruntal (Olomoucky/Moravskoslezsky). Dolní Benešov = mesto v okrese Opava (Moravskoslezsky). Brano = Brany podnik (Horni Benesov, vyroba dveri). MSA = Moravskoslezska armaturka (Dolni Benesov). Wiki D42 - Pavlovo upresneni 04/2026. city Horní Benešov / Dolní Benešov (NIKDY neni Stredocesky Benesov). || Horní Benešov = Spartak Horní Benešov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntal). POZOR: Dolni Benesov u Opavy! Vsichni Benešovi v okrese - Horni, Dolni, Benesov u Prahy. city Horní Benešov.</t>
+          <t>Opava = HC B.D. Opava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. PARSING: B.D. zkracene. city Opava.</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>B.D. Opava</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0430</t>
+          <t>CLUB_S1995_96_0431</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>B.D. Opava</t>
+          <t>Jiskra Rýmařov</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>B.D. Opava</t>
+          <t>Jiskra Rýmařov (S)</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -44477,36 +44610,51 @@
           <t>30_Severomoravský</t>
         </is>
       </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>L40</t>
+          <t>okresní</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Bruntál</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0321</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>Opava = HC B.D. Opava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. PARSING: B.D. zkracene. city Opava.</t>
+          <t>Sloučení duplicit: kolega měl klub 2× pro různé fáze KS (skupina B + o udržení), automat dal 2 různé cid. Sloučeno: zachovat CLUB_S1954_55_0648, smazat CLUB_S1954_55_0665. || Rýmařov = Banik/Jiskra Rýmařov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntal). Patterns: Sokol -&gt; Jiskra -&gt; Banik -&gt; Dukla Rýmařov (vojensky paralelni). city Rýmařov.</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>B.D. Opava</t>
+          <t>Rýmařov</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0431</t>
+          <t>CLUB_S1995_96_0432</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Jiskra Rýmařov</t>
+          <t>Valšov</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Jiskra Rýmařov (S)</t>
+          <t>Valšov</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -44514,11 +44662,6 @@
           <t>30_Severomoravský</t>
         </is>
       </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
       <c r="F417" t="inlineStr">
         <is>
           <t>okresní</t>
@@ -44529,36 +44672,31 @@
           <t>Bruntál</t>
         </is>
       </c>
-      <c r="H417" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0321</t>
-        </is>
-      </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>Sloučení duplicit: kolega měl klub 2× pro různé fáze KS (skupina B + o udržení), automat dal 2 různé cid. Sloučeno: zachovat CLUB_S1954_55_0648, smazat CLUB_S1954_55_0665. || Rýmařov = Banik/Jiskra Rýmařov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntal). Patterns: Sokol -&gt; Jiskra -&gt; Banik -&gt; Dukla Rýmařov (vojensky paralelni). city Rýmařov.</t>
+          <t>Valšov = TJ Sokol Valšov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntál). city Valšov.</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>Rýmařov</t>
+          <t>Valšov</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0432</t>
+          <t>CLUB_S1995_96_0433</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Valšov</t>
+          <t>N.Rýmařov</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Valšov</t>
+          <t>N.Rýmařov</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -44576,31 +44714,36 @@
           <t>Bruntál</t>
         </is>
       </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0321</t>
+        </is>
+      </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>Valšov = TJ Sokol Valšov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntál). city Valšov.</t>
+          <t>Sloučení duplicit: kolega měl klub 2× pro různé fáze KS (skupina B + o udržení), automat dal 2 různé cid. Sloučeno: zachovat CLUB_S1954_55_0648, smazat CLUB_S1954_55_0665. || Rýmařov = Banik/Jiskra Rýmařov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntal). Patterns: Sokol -&gt; Jiskra -&gt; Banik -&gt; Dukla Rýmařov (vojensky paralelni). city Rýmařov.</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>Valšov</t>
+          <t>Rýmařov</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0433</t>
+          <t>CLUB_S1995_96_0434</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>N.Rýmařov</t>
+          <t>Horní Benešov B</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>N.Rýmařov</t>
+          <t>Horní Benešov B</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -44620,34 +44763,34 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0321</t>
+          <t>CLUB_S1994_95_0320</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>Sloučení duplicit: kolega měl klub 2× pro různé fáze KS (skupina B + o udržení), automat dal 2 různé cid. Sloučeno: zachovat CLUB_S1954_55_0648, smazat CLUB_S1954_55_0665. || Rýmařov = Banik/Jiskra Rýmařov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntal). Patterns: Sokol -&gt; Jiskra -&gt; Banik -&gt; Dukla Rýmařov (vojensky paralelni). city Rýmařov.</t>
+          <t>Brano Horní Benešov 52/53 (20_Ostravský). Brano = strojirensky podnik. Horní Benešov + Dolní Benešov = JINE MESTO od Benesov u Prahy (Stredocesky)! Horní Benešov / Dolní Benešov jsou obce ve Slezsku (Bruntal/Opava) - Ostravsky kraj. Brano Horní Benešov = strojirensky podnik Brano. MSA Dolní Benešov = MSA strojirenstvi. Wiki D42 - Pavlovo upresneni 04/2026. NE Benesov u Prahy chain! || Brano Horní Benešov 52/53 (20_Ostravský). Brano = Brany podnik. Horní Benešov / Dolní Benešov = JINÉ MĚSTO od Benešov (Stredocesky). Horní Benešov = mesto v okrese Bruntal (Olomoucky/Moravskoslezsky). Dolní Benešov = mesto v okrese Opava (Moravskoslezsky). Brano = Brany podnik (Horni Benesov, vyroba dveri). MSA = Moravskoslezska armaturka (Dolni Benesov). Wiki D42 - Pavlovo upresneni 04/2026. city Horní Benešov / Dolní Benešov (NIKDY neni Stredocesky Benesov). || Horní Benešov = Spartak Horní Benešov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntal). POZOR: Dolni Benesov u Opavy! Vsichni Benešovi v okrese - Horni, Dolni, Benesov u Prahy. city Horní Benešov.</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>Rýmařov</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0434</t>
+          <t>CLUB_S1995_96_0435</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Horní Benešov B</t>
+          <t>SOU Horní Benešov</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Horní Benešov B</t>
+          <t>SOU Horní Benešov</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -44684,17 +44827,17 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0435</t>
+          <t>CLUB_S1995_96_0436</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>SOU Horní Benešov</t>
+          <t>Med. Rýmařov</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>SOU Horní Benešov</t>
+          <t>Med. Rýmařov</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -44714,34 +44857,34 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0320</t>
+          <t>CLUB_S1994_95_0321</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>Brano Horní Benešov 52/53 (20_Ostravský). Brano = strojirensky podnik. Horní Benešov + Dolní Benešov = JINE MESTO od Benesov u Prahy (Stredocesky)! Horní Benešov / Dolní Benešov jsou obce ve Slezsku (Bruntal/Opava) - Ostravsky kraj. Brano Horní Benešov = strojirensky podnik Brano. MSA Dolní Benešov = MSA strojirenstvi. Wiki D42 - Pavlovo upresneni 04/2026. NE Benesov u Prahy chain! || Brano Horní Benešov 52/53 (20_Ostravský). Brano = Brany podnik. Horní Benešov / Dolní Benešov = JINÉ MĚSTO od Benešov (Stredocesky). Horní Benešov = mesto v okrese Bruntal (Olomoucky/Moravskoslezsky). Dolní Benešov = mesto v okrese Opava (Moravskoslezsky). Brano = Brany podnik (Horni Benesov, vyroba dveri). MSA = Moravskoslezska armaturka (Dolni Benesov). Wiki D42 - Pavlovo upresneni 04/2026. city Horní Benešov / Dolní Benešov (NIKDY neni Stredocesky Benesov). || Horní Benešov = Spartak Horní Benešov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntal). POZOR: Dolni Benesov u Opavy! Vsichni Benešovi v okrese - Horni, Dolni, Benesov u Prahy. city Horní Benešov.</t>
+          <t>Sloučení duplicit: kolega měl klub 2× pro různé fáze KS (skupina B + o udržení), automat dal 2 různé cid. Sloučeno: zachovat CLUB_S1954_55_0648, smazat CLUB_S1954_55_0665. || Rýmařov = Banik/Jiskra Rýmařov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntal). Patterns: Sokol -&gt; Jiskra -&gt; Banik -&gt; Dukla Rýmařov (vojensky paralelni). city Rýmařov.</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Rýmařov</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0436</t>
+          <t>CLUB_S1995_96_0437</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Med. Rýmařov</t>
+          <t>Svatá Hora</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Med. Rýmařov</t>
+          <t>Svatá Hora</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -44759,36 +44902,31 @@
           <t>Bruntál</t>
         </is>
       </c>
-      <c r="H422" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0321</t>
-        </is>
-      </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>Sloučení duplicit: kolega měl klub 2× pro různé fáze KS (skupina B + o udržení), automat dal 2 různé cid. Sloučeno: zachovat CLUB_S1954_55_0648, smazat CLUB_S1954_55_0665. || Rýmařov = Banik/Jiskra Rýmařov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntal). Patterns: Sokol -&gt; Jiskra -&gt; Banik -&gt; Dukla Rýmařov (vojensky paralelni). city Rýmařov.</t>
+          <t>Svatá Hora = TJ Sokol Svatá Hora (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (Pribram - poutni misto). city Svatá Hora u Příbrami.</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>Rýmařov</t>
+          <t>Svatá Hora</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0437</t>
+          <t>CLUB_S1995_96_0438</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Svatá Hora</t>
+          <t>M.Morávka</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Svatá Hora</t>
+          <t>M.Morávka</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -44808,29 +44946,29 @@
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>Svatá Hora = TJ Sokol Svatá Hora (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (Pribram - poutni misto). city Svatá Hora u Příbrami.</t>
+          <t>Malá Morávka = TJ Sokol Malá Morávka (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntál). PARSING CHYBA: 'M.' zkracene. city Malá Morávka.</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>Svatá Hora</t>
+          <t>M.Morávka</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0438</t>
+          <t>CLUB_S1995_96_0439</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>M.Morávka</t>
+          <t>Las Vegas Krnov</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>M.Morávka</t>
+          <t>Las Vegas Krnov</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -44845,34 +44983,34 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Bruntál</t>
+          <t>Krnov</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>Malá Morávka = TJ Sokol Malá Morávka (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntál). PARSING CHYBA: 'M.' zkracene. city Malá Morávka.</t>
+          <t>Krnov = HC Las Vegas Krnov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Post-revolucni humorny nazev (USA mesto). city Krnov. || TBD: city 'Las Vegas Krnov' → 'Krnov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>M.Morávka</t>
+          <t>Krnov</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0439</t>
+          <t>CLUB_S1995_96_0440</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Las Vegas Krnov</t>
+          <t>Opole</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Las Vegas Krnov</t>
+          <t>Opole</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -44892,29 +45030,29 @@
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>Krnov = HC Las Vegas Krnov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Post-revolucni humorny nazev (USA mesto). city Krnov. || TBD: city 'Las Vegas Krnov' → 'Krnov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>Opole = HC Opole (Wiki D42 - registr ustavy 04/2026). **Opole = mesto v Polsku** (Slezsko). Pohranicni klub Krnovsky region. city Opole.</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>Krnov</t>
+          <t>Opole</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0440</t>
+          <t>CLUB_S1995_96_0441</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Pega Krnov</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Pega Krnov</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -44934,29 +45072,29 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>Opole = HC Opole (Wiki D42 - registr ustavy 04/2026). **Opole = mesto v Polsku** (Slezsko). Pohranicni klub Krnovsky region. city Opole.</t>
+          <t>Krnov = HC Pega Krnov (Wiki D42 - registr ustavy 04/2026). Severomoravsky kraj. **Pega** = sponzor. city Krnov.</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Pega Krnov</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0441</t>
+          <t>CLUB_S1995_96_0442</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Pega Krnov</t>
+          <t>Olejáři Krnov</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Pega Krnov</t>
+          <t>Olejáři Krnov</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -44976,29 +45114,29 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>Krnov = HC Pega Krnov (Wiki D42 - registr ustavy 04/2026). Severomoravsky kraj. **Pega** = sponzor. city Krnov.</t>
+          <t>Krnov = HC Olejáři Krnov (Wiki D42 - registr ustavy 04/2026). Severomoravsky kraj. **Olejáři** = oleje, sponzor. city Krnov.</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>Pega Krnov</t>
+          <t>Olejáři Krnov</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0442</t>
+          <t>CLUB_S1995_96_0443</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Olejáři Krnov</t>
+          <t>Mikoss Krnov</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Olejáři Krnov</t>
+          <t>Mikoss Krnov</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -45018,29 +45156,29 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>Krnov = HC Olejáři Krnov (Wiki D42 - registr ustavy 04/2026). Severomoravsky kraj. **Olejáři** = oleje, sponzor. city Krnov.</t>
+          <t>Krnov = HC Mikoss Krnov (Wiki D42 - registr ustavy 04/2026). Severomoravsky kraj. **Mikoss** = sponzor. city Krnov.</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>Olejáři Krnov</t>
+          <t>Mikoss Krnov</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0443</t>
+          <t>CLUB_S1995_96_0444</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Mikoss Krnov</t>
+          <t>Tučnáci Krnov</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Mikoss Krnov</t>
+          <t>Tučnáci Krnov</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -45060,29 +45198,29 @@
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>Krnov = HC Mikoss Krnov (Wiki D42 - registr ustavy 04/2026). Severomoravsky kraj. **Mikoss** = sponzor. city Krnov.</t>
+          <t>Krnov = HC Tučnáci Krnov (Wiki D42 - registr ustavy 04/2026). Severomoravsky kraj. Humorny nazev. city Krnov.</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>Mikoss Krnov</t>
+          <t>Tučnáci Krnov</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0444</t>
+          <t>CLUB_S1995_96_0445</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Tučnáci Krnov</t>
+          <t>HC Špica Krnov</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Tučnáci Krnov</t>
+          <t>HC Špica Krnov</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -45100,31 +45238,36 @@
           <t>Krnov</t>
         </is>
       </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0067</t>
+        </is>
+      </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>Krnov = HC Tučnáci Krnov (Wiki D42 - registr ustavy 04/2026). Severomoravsky kraj. Humorny nazev. city Krnov.</t>
+          <t>Krnov = TJ Strojsvit Krnov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Strojsvit** = strojirensky podnik (vyrobce sicich stroju - Krnov mela Bystrice/Minerva). city Krnov.</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>Tučnáci Krnov</t>
+          <t>Strojsvit Krnov</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0445</t>
+          <t>CLUB_S1995_96_0446</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>HC Špica Krnov</t>
+          <t>Strojsvit Krnov dorost</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>HC Špica Krnov</t>
+          <t>Strojsvit Krnov dorost</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -45161,17 +45304,17 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0446</t>
+          <t>CLUB_S1995_96_0447</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Strojsvit Krnov dorost</t>
+          <t>Věrovany</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Strojsvit Krnov dorost</t>
+          <t>Věrovany</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -45186,39 +45329,34 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Krnov</t>
-        </is>
-      </c>
-      <c r="H432" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0067</t>
+          <t>Olomouc</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>Krnov = TJ Strojsvit Krnov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Strojsvit** = strojirensky podnik (vyrobce sicich stroju - Krnov mela Bystrice/Minerva). city Krnov.</t>
+          <t>Věrovany = TJ Sokol Věrovany (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Olomouc). city Věrovany.</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>Strojsvit Krnov</t>
+          <t>Věrovany</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0447</t>
+          <t>CLUB_S1995_96_0448</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Věrovany</t>
+          <t>Lutín</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Věrovany</t>
+          <t>Lutín</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -45238,29 +45376,29 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>Věrovany = TJ Sokol Věrovany (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Olomouc). city Věrovany.</t>
+          <t>Lutín = TJ Spartak Sigma Lutín (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. **Sigma Lutín** = vyrobce cerpadel. 'OLO' = Olomouc skupina. city Lutín.</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>Věrovany</t>
+          <t>Lutín</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0448</t>
+          <t>CLUB_S1995_96_0449</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Lutín</t>
+          <t>M. Olomouc</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Lutín</t>
+          <t>M. Olomouc</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -45280,29 +45418,29 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>Lutín = TJ Spartak Sigma Lutín (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. **Sigma Lutín** = vyrobce cerpadel. 'OLO' = Olomouc skupina. city Lutín.</t>
+          <t>Olomouc = HC M.Olomouc (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. PARSING CHYBA: 'M.' zkracene. city Olomouc.</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>Lutín</t>
+          <t>M. Olomouc</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0449</t>
+          <t>CLUB_S1995_96_0450</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>M. Olomouc</t>
+          <t>Hynkov</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>M. Olomouc</t>
+          <t>Hynkov</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -45322,29 +45460,29 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>Olomouc = HC M.Olomouc (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. PARSING CHYBA: 'M.' zkracene. city Olomouc.</t>
+          <t>Hynkov = TJ Sokol Hynkov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Olomouc). city Hynkov.</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>M. Olomouc</t>
+          <t>Hynkov</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0450</t>
+          <t>CLUB_S1995_96_0451</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Hynkov</t>
+          <t>Tršice</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Hynkov</t>
+          <t>Tršice</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -45364,29 +45502,29 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>Hynkov = TJ Sokol Hynkov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Olomouc). city Hynkov.</t>
+          <t>Sokol Tršice (Olomouc venkov, jako 58/59 0624). Oprava clean+city: "Trštice" → "Tršice" (preklep almanachu). || Tršice = TJ Sokol Tršice (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Olomouc). city Tršice.</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>Hynkov</t>
+          <t>Tršice</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0451</t>
+          <t>CLUB_S1995_96_0452</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Tršice</t>
+          <t>Těšetice</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Tršice</t>
+          <t>Těšetice</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -45406,29 +45544,29 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>Sokol Tršice (Olomouc venkov, jako 58/59 0624). Oprava clean+city: "Trštice" → "Tršice" (preklep almanachu). || Tršice = TJ Sokol Tršice (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Olomouc). city Tršice.</t>
+          <t>Těšetice = TJ Sokol Těšetice (Wiki D42 - registr ustavy 04/2026). 30_oblastni sezona 55/56 - oblastni soutez, nelze rozlisit. POZOR: vícero - Těšetice u Olomouce (Severomoravsko), Těšetice u Znojma (Jihomoravsko), Těšetice u Vyskova. K overeni. city Těšetice.</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>Tršice</t>
+          <t>Těšetice</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0452</t>
+          <t>CLUB_S1995_96_0453</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Těšetice</t>
+          <t>Slezan Opava Old Boys</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Těšetice</t>
+          <t>Slezan Opava Old Boys</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -45443,34 +45581,39 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0019</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>Těšetice = TJ Sokol Těšetice (Wiki D42 - registr ustavy 04/2026). 30_oblastni sezona 55/56 - oblastni soutez, nelze rozlisit. POZOR: vícero - Těšetice u Olomouce (Severomoravsko), Těšetice u Znojma (Jihomoravsko), Těšetice u Vyskova. K overeni. city Těšetice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>Těšetice</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0453</t>
+          <t>CLUB_S1995_96_0454</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Slezan Opava Old Boys</t>
+          <t>M. Hoštice</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Slezan Opava Old Boys</t>
+          <t>M. Hoštice</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -45488,36 +45631,31 @@
           <t>Opava</t>
         </is>
       </c>
-      <c r="H439" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0019</t>
-        </is>
-      </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Moravské Hoštice = TJ Sokol M.Hoštice (Wiki D42 - registr ustavy 04/2026). PARSING CHYBA: 'M.' = Moravské. K overeni - mozna Šumavske Hoštice nebo jine. K overeni. city Moravské Hoštice.</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>M. Hoštice</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0454</t>
+          <t>CLUB_S1995_96_0455</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>M. Hoštice</t>
+          <t>Měst.policie Opava</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>M. Hoštice</t>
+          <t>Měst.policie Opava</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -45537,29 +45675,29 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>Moravské Hoštice = TJ Sokol M.Hoštice (Wiki D42 - registr ustavy 04/2026). PARSING CHYBA: 'M.' = Moravské. K overeni - mozna Šumavske Hoštice nebo jine. K overeni. city Moravské Hoštice.</t>
+          <t>Opava = HC Měst.policie Opava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Mestska policie** Opavy. city Opava.</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>M. Hoštice</t>
+          <t>Měst.policie Opava</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0455</t>
+          <t>CLUB_S1995_96_0456</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Měst.policie Opava</t>
+          <t>Otice</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Měst.policie Opava</t>
+          <t>Otice</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -45579,29 +45717,29 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>Opava = HC Měst.policie Opava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Mestska policie** Opavy. city Opava.</t>
+          <t>city ✓ (vesnice u Opavy). || Otice = Sokol Otice (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). city Otice.</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>Měst.policie Opava</t>
+          <t>Otice</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0456</t>
+          <t>CLUB_S1995_96_0457</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Otice</t>
+          <t>Parmalat Opava</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Otice</t>
+          <t>Parmalat Opava</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -45621,29 +45759,29 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>city ✓ (vesnice u Opavy). || Otice = Sokol Otice (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). city Otice.</t>
+          <t>Opava = HC Parmalat Opava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Parmalat** = italska mleciarska firma (sponzor). city Opava.</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>Otice</t>
+          <t>Parmalat Opava</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0457</t>
+          <t>CLUB_S1995_96_0458</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Parmalat Opava</t>
+          <t>SK Policie Opava</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Parmalat Opava</t>
+          <t>SK Policie Opava</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -45663,29 +45801,29 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>Opava = HC Parmalat Opava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Parmalat** = italska mleciarska firma (sponzor). city Opava.</t>
+          <t>Opava = SK Policie Opava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. city Opava.</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>Parmalat Opava</t>
+          <t>Policie Opava</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0458</t>
+          <t>CLUB_S1995_96_0459</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>SK Policie Opava</t>
+          <t>Newvers Rangers Ostrava</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>SK Policie Opava</t>
+          <t>Newvers Rangers Ostrava</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -45700,34 +45838,34 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>skupina A</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>Opava = SK Policie Opava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. city Opava.</t>
+          <t>Ostrava = HC Newvers Rangers Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Post-revolucni anglicky nazev. city Ostrava. || TBD: city 'Newvers Rangers Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>Policie Opava</t>
+          <t>Ostrava</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0459</t>
+          <t>CLUB_S1995_96_0460</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Newvers Rangers Ostrava</t>
+          <t>Amatér Ostrava</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Newvers Rangers Ostrava</t>
+          <t>Amatér Ostrava</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -45747,29 +45885,29 @@
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>Ostrava = HC Newvers Rangers Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Post-revolucni anglicky nazev. city Ostrava. || TBD: city 'Newvers Rangers Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>Ostrava = HC Amatér Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. city Ostrava.</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>Ostrava</t>
+          <t>Amatér Ostrava</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0460</t>
+          <t>CLUB_S1995_96_0461</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Amatér Ostrava</t>
+          <t>GCO Ostrava</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Amatér Ostrava</t>
+          <t>GCO Ostrava</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -45789,29 +45927,29 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>Ostrava = HC Amatér Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. city Ostrava.</t>
+          <t>Ostrava = HC GCO Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. city Ostrava.</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>Amatér Ostrava</t>
+          <t>GCO Ostrava</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0461</t>
+          <t>CLUB_S1995_96_0462</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>GCO Ostrava</t>
+          <t>NH Válcovny Ostrava</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>GCO Ostrava</t>
+          <t>NH Válcovny Ostrava</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -45831,29 +45969,29 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>Ostrava = HC GCO Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. city Ostrava.</t>
+          <t>Ostrava = TJ NH Válcovny Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **NH** = Nová huť. **Válcovny** = oddeleni NH. city Ostrava. || TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>GCO Ostrava</t>
+          <t>Ostrava</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0462</t>
+          <t>CLUB_S1995_96_0463</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>NH Válcovny Ostrava</t>
+          <t>Závod 10 Koksovna</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>NH Válcovny Ostrava</t>
+          <t>Závod 10 Koksovna</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -45873,29 +46011,29 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>Ostrava = TJ NH Válcovny Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **NH** = Nová huť. **Válcovny** = oddeleni NH. city Ostrava. || TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>Ostrava = TJ Závod 10 Koksovna (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Koksovna** = soucast NHKG/NH Ostrava. city Ostrava.</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>Ostrava</t>
+          <t>Závod 10 Koksovna</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0463</t>
+          <t>CLUB_S1995_96_0464</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Závod 10 Koksovna</t>
+          <t>Star Ostrava</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Závod 10 Koksovna</t>
+          <t>Star Ostrava</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -45915,29 +46053,29 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>Ostrava = TJ Závod 10 Koksovna (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Koksovna** = soucast NHKG/NH Ostrava. city Ostrava.</t>
+          <t>Ostrava = HC Star Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Post-revolucni. city Ostrava.</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>Závod 10 Koksovna</t>
+          <t>Star Ostrava</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0464</t>
+          <t>CLUB_S1995_96_0465</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Star Ostrava</t>
+          <t>Sport club Ostrava</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Star Ostrava</t>
+          <t>Sport club Ostrava</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -45952,34 +46090,34 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>skupina A</t>
+          <t>skupina B</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>Ostrava = HC Star Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Post-revolucni. city Ostrava.</t>
+          <t>Ostrava = Sport club Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. city Ostrava. || TBD: city 'Sport club Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>Star Ostrava</t>
+          <t>Ostrava</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0465</t>
+          <t>CLUB_S1995_96_0466</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Sport club Ostrava</t>
+          <t>Bítov</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Sport club Ostrava</t>
+          <t>Bítov</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -45999,29 +46137,29 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>Ostrava = Sport club Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. city Ostrava. || TBD: city 'Sport club Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>Bítov = TJ Bítov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). Hradni mesto (Bitov hrad nad Vranovskou prehradou). city Bítov.</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>Ostrava</t>
+          <t>Bítov</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0466</t>
+          <t>CLUB_S1995_96_0467</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Bítov</t>
+          <t>Jestřábí</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Bítov</t>
+          <t>Jestřábí</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -46041,29 +46179,29 @@
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>Bítov = TJ Bítov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). Hradni mesto (Bitov hrad nad Vranovskou prehradou). city Bítov.</t>
+          <t>Jestřebí = TJ Sokol Jestřebí (Wiki D42 - registr ustavy 04/2026). PARSING CHYBA: 'Jestřábí' varianta 'Jestřebí'. POZOR: vícero - Jestřebí u České Lipy (Severocesko), Jestřebí v Krkonosich. K overeni. city Jestřebí.</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>Bítov</t>
+          <t>Jestřábí</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0467</t>
+          <t>CLUB_S1995_96_0468</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Jestřábí</t>
+          <t>Heřmanice</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Jestřábí</t>
+          <t>Heřmanice</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -46083,29 +46221,29 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>Jestřebí = TJ Sokol Jestřebí (Wiki D42 - registr ustavy 04/2026). PARSING CHYBA: 'Jestřábí' varianta 'Jestřebí'. POZOR: vícero - Jestřebí u České Lipy (Severocesko), Jestřebí v Krkonosich. K overeni. city Jestřebí.</t>
+          <t>Heřmanice = TJ Sokol Heřmanice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero - Heřmanice (Severomoravsky/Ostrava-mc), Heřmanice u Frýdlantu (Severocesky), Heřmanice nL Labem (Severomoravsky/Decin). K overeni. city Heřmanice.</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>Jestřábí</t>
+          <t>Heřmanice</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0468</t>
+          <t>CLUB_S1995_96_0469</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Heřmanice</t>
+          <t>DPMO Hranečník</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Heřmanice</t>
+          <t>DPMO Hranečník</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -46125,29 +46263,29 @@
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>Heřmanice = TJ Sokol Heřmanice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero - Heřmanice (Severomoravsky/Ostrava-mc), Heřmanice u Frýdlantu (Severocesky), Heřmanice nL Labem (Severomoravsky/Decin). K overeni. city Heřmanice.</t>
+          <t>Ostrava (Hranečník) = TJ DPMO Hranečník (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **DPMO** = Dopravni podnik mesta Ostravy. Hranečník = mestska cast Ostravy. city Ostrava (Hranečník).</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>Heřmanice</t>
+          <t>DPMO Hranečník</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0469</t>
+          <t>CLUB_S1995_96_0470</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>DPMO Hranečník</t>
+          <t>Milenov</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>DPMO Hranečník</t>
+          <t>Milenov</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -46162,34 +46300,39 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>skupina B</t>
+          <t>Přerov</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0273</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>Ostrava (Hranečník) = TJ DPMO Hranečník (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **DPMO** = Dopravni podnik mesta Ostravy. Hranečník = mestska cast Ostravy. city Ostrava (Hranečník).</t>
+          <t>Milenov = TJ Sokol Milenov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Přerov). city Milenov.</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>DPMO Hranečník</t>
+          <t>Milenov</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0470</t>
+          <t>CLUB_S1995_96_0471</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Milenov</t>
+          <t>Citov</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Milenov</t>
+          <t>Citov</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -46209,34 +46352,34 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0273</t>
+          <t>CLUB_S1994_95_0276</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>Milenov = TJ Sokol Milenov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Přerov). city Milenov.</t>
+          <t>Citov = TJ Sokol Citov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Přerov). city Citov.</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>Milenov</t>
+          <t>Citov</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0471</t>
+          <t>CLUB_S1995_96_0472</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Citov</t>
+          <t>Zborovice</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Citov</t>
+          <t>Zborovice</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -46256,34 +46399,34 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0276</t>
+          <t>CLUB_S1994_95_0274</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>Citov = TJ Sokol Citov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Přerov). city Citov.</t>
+          <t>Zborovice - almanach bez prefixu (D35, Kroměříž). || Zborovice = TJ Spartak Zborovice (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (okres Kroměříž). Patterns: Sokol -&gt; Spartak Zborovice. city Zborovice.</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>Citov</t>
+          <t>Zborovice</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0472</t>
+          <t>CLUB_S1995_96_0473</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Zborovice</t>
+          <t>Chomýž</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Zborovice</t>
+          <t>Chomýž</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -46303,34 +46446,34 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0274</t>
+          <t>CLUB_S1994_95_0277</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>Zborovice - almanach bez prefixu (D35, Kroměříž). || Zborovice = TJ Spartak Zborovice (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (okres Kroměříž). Patterns: Sokol -&gt; Spartak Zborovice. city Zborovice.</t>
+          <t>Chomýž u Kroměříže = TJ Sokol Chomýž (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (okres Kroměříž, district 'Kroměříž' potvrzen). POZOR: vícero - Chomýž u Krnova (Severomoravsky/Bruntál), Chomýž u Bruntálu. city Chomýž u Kroměříže.</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>Zborovice</t>
+          <t>Chomýž</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0473</t>
+          <t>CLUB_S1995_96_0474</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Chomýž</t>
+          <t>Troubky</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Chomýž</t>
+          <t>Troubky</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -46350,34 +46493,34 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0277</t>
+          <t>CLUB_S1994_95_0275</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>Chomýž u Kroměříže = TJ Sokol Chomýž (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (okres Kroměříž, district 'Kroměříž' potvrzen). POZOR: vícero - Chomýž u Krnova (Severomoravsky/Bruntál), Chomýž u Bruntálu. city Chomýž u Kroměříže.</t>
+          <t>Sloučení duplicit: kolega měl klub 2× pro různé fáze KS (skupina B + o udržení), automat dal 2 různé cid. Sloučeno: zachovat CLUB_S1954_55_0642, smazat CLUB_S1954_55_0669. || Troubky = Sokol Troubky nL Bečvou (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Přerov). PŘE = Přerov. city Troubky.</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>Chomýž</t>
+          <t>Troubky</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0474</t>
+          <t>CLUB_S1995_96_0475</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Troubky</t>
+          <t>Kojetín</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Troubky</t>
+          <t>Kojetín</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -46397,34 +46540,34 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>CLUB_S1994_95_0275</t>
+          <t>CLUB_S1994_95_0278</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>Sloučení duplicit: kolega měl klub 2× pro různé fáze KS (skupina B + o udržení), automat dal 2 různé cid. Sloučeno: zachovat CLUB_S1954_55_0642, smazat CLUB_S1954_55_0669. || Troubky = Sokol Troubky nL Bečvou (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Přerov). PŘE = Přerov. city Troubky.</t>
+          <t>city ✓ (město u Přerova). || Kojetín = Slavoj Kojetín (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Prerov). city Kojetín.</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>Troubky</t>
+          <t>Kojetín</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0475</t>
+          <t>CLUB_S1995_96_0476</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Kojetín</t>
+          <t>Třemešek</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Kojetín</t>
+          <t>Třemešek</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -46439,39 +46582,34 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>Přerov</t>
-        </is>
-      </c>
-      <c r="H461" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0278</t>
+          <t>Šumperk</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>city ✓ (město u Přerova). || Kojetín = Slavoj Kojetín (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Prerov). city Kojetín.</t>
+          <t>Třemešek = TJ Sokol Třemešek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Šumperk). city Třemešek.</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>Kojetín</t>
+          <t>Třemešek</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0476</t>
+          <t>CLUB_S1995_96_0477</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Třemešek</t>
+          <t>Ruda</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Třemešek</t>
+          <t>Ruda</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -46491,29 +46629,29 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>Třemešek = TJ Sokol Třemešek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Šumperk). city Třemešek.</t>
+          <t>Ruda = TJ Sokol Ruda (Wiki D42 - registr ustavy 04/2026). POZOR: vícero - Ruda nad Moravou (Severomoravsko/Olomouc), Ruda u Velkého Meziříčí. K overeni. city Ruda.</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>Třemešek</t>
+          <t>Ruda</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0477</t>
+          <t>CLUB_S1995_96_0478</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Ruda</t>
+          <t>Mohelnice</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Ruda</t>
+          <t>Mohelnice</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -46533,29 +46671,29 @@
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>Ruda = TJ Sokol Ruda (Wiki D42 - registr ustavy 04/2026). POZOR: vícero - Ruda nad Moravou (Severomoravsko/Olomouc), Ruda u Velkého Meziříčí. K overeni. city Ruda.</t>
+          <t>city ✓ (město u Šumperka). || Mohelnice = Spartak Mohelnice (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Šumperk). city Mohelnice.</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>Ruda</t>
+          <t>Mohelnice</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0478</t>
+          <t>CLUB_S1995_96_0479</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Mohelnice</t>
+          <t>Hrabišín</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Mohelnice</t>
+          <t>Hrabišín</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -46575,29 +46713,29 @@
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>city ✓ (město u Šumperka). || Mohelnice = Spartak Mohelnice (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Šumperk). city Mohelnice.</t>
+          <t>Hrabišín = TJ Sokol Hrabišín (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Sumperk). city Hrabišín.</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>Mohelnice</t>
+          <t>Hrabišín</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0479</t>
+          <t>CLUB_S1995_96_0480</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Hrabišín</t>
+          <t>Dubnicko</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Hrabišín</t>
+          <t>Dubnicko</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -46617,29 +46755,29 @@
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>Hrabišín = TJ Sokol Hrabišín (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Sumperk). city Hrabišín.</t>
+          <t>Dubnicko = TJ Sokol Dubnicko (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Šumperk). city Dubnicko.</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>Hrabišín</t>
+          <t>Dubnicko</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0480</t>
+          <t>CLUB_S1995_96_0481</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Dubnicko</t>
+          <t>Vikýřovice</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Dubnicko</t>
+          <t>Vikýřovice</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -46659,71 +46797,71 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>Dubnicko = TJ Sokol Dubnicko (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Šumperk). city Dubnicko.</t>
+          <t>Vikýřovice = TJ Sokol Vikýřovice (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Šumperk). city Vikýřovice.</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>Dubnicko</t>
+          <t>Vikýřovice</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0481</t>
+          <t>CLUB_S1995_96_0483</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Vikýřovice</t>
+          <t>HC Slovan Louny</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Vikýřovice</t>
+          <t>HC Slovan Louny</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>30_Severomoravský</t>
+          <t>KVAL</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>okresní</t>
-        </is>
-      </c>
-      <c r="G467" t="inlineStr">
-        <is>
-          <t>Šumperk</t>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>CLUB_S1994_95_0175</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>Vikýřovice = TJ Sokol Vikýřovice (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Šumperk). city Vikýřovice.</t>
+          <t>Oprava city: „Louky" → „Louky (UNL)". TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo. || Oprava clean+city: "Louky" → "Louny" (překlep almanachu, Pavlovo upresneni 04/2026 - district "skupina B" v Ústeckém kraji = okres Louny). prev=CLUB_S1951_52_0427 byl chybný (ukazoval na Karviná) - k overeni Pavlem. || Louny = Slovan Louny (Wiki D42 - registr ustavy 04/2026). Hlavni okresni klub. Genealogie: Cechie Louny (49/50) -&gt; VSJ -&gt; Slovan Louny. city Louny. || TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>Vikýřovice</t>
+          <t>Louny</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0483</t>
+          <t>CLUB_S1995_96_0484</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>HC Slovan Louny</t>
+          <t>HBH Holešák Havlíčkův Brod</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>HC Slovan Louny</t>
+          <t>HBH Holešák Havlíčkův Brod</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -46736,36 +46874,31 @@
           <t>L25</t>
         </is>
       </c>
-      <c r="H468" t="inlineStr">
-        <is>
-          <t>CLUB_S1994_95_0175</t>
-        </is>
-      </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>Oprava city: „Louky" → „Louky (UNL)". TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo. || Oprava clean+city: "Louky" → "Louny" (překlep almanachu, Pavlovo upresneni 04/2026 - district "skupina B" v Ústeckém kraji = okres Louny). prev=CLUB_S1951_52_0427 byl chybný (ukazoval na Karviná) - k overeni Pavlem. || Louny = Slovan Louny (Wiki D42 - registr ustavy 04/2026). Hlavni okresni klub. Genealogie: Cechie Louny (49/50) -&gt; VSJ -&gt; Slovan Louny. city Louny. || TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>Havlíčkův Brod = HBH Holešák Havlíčkův Brod (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **HBH Holešák** = post-revolucni nazev. city Havlíčkův Brod. || TBD: city 'Holešák Havlíčkův Brod' → 'Havlíčkův Brod' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>Louny</t>
+          <t>Havlíčkův Brod</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0484</t>
+          <t>CLUB_S1995_96_0485</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>HBH Holešák Havlíčkův Brod</t>
+          <t>HC Uherské Hradiště</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>HBH Holešák Havlíčkův Brod</t>
+          <t>HC Uherské Hradiště</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -46780,29 +46913,29 @@
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod = HBH Holešák Havlíčkův Brod (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **HBH Holešák** = post-revolucni nazev. city Havlíčkův Brod. || TBD: city 'Holešák Havlíčkův Brod' → 'Havlíčkův Brod' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>Spartak Uherské Hradiště. city ✓. || Uherské Hradiště (Wiki - registr ustavy 04/2026). Jihomoravsky/Zlinsky kraj. POZN: blizko Uherskeho Hradiste byly Sokol Stare Mesto, Tatran Uhersky Ostroh atd. city Uherské Hradiště.</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0485</t>
+          <t>CLUB_S1995_96_0486</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>HC Uherské Hradiště</t>
+          <t>TJ Poděbrady</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>HC Uherské Hradiště</t>
+          <t>TJ Poděbrady</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -46817,79 +46950,42 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>Spartak Uherské Hradiště. city ✓. || Uherské Hradiště (Wiki - registr ustavy 04/2026). Jihomoravsky/Zlinsky kraj. POZN: blizko Uherskeho Hradiste byly Sokol Stare Mesto, Tatran Uhersky Ostroh atd. city Uherské Hradiště.</t>
+          <t>Oprava city: „Sklárny Poděbrady" → „Poděbrady" (Sklárny = závod). || Poděbrady = Jiskra Poděbrady / HC Poděbrady (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Nymburk). Sklarny Podebrady = sklarsky podnik. Patterns: Sokol -&gt; DSO Jiskra -&gt; TJ Jiskra Poděbrady. city Poděbrady.</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>Uherské Hradiště</t>
+          <t>Poděbrady</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0486</t>
+          <t>CLUB_S1995_96_0319</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>TJ Poděbrady</t>
+          <t>čtvrtfinále</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>TJ Poděbrady</t>
+          <t>čtvrtfinále</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>KVAL</t>
+          <t>30VYCH</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L100</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
-        <is>
-          <t>Oprava city: „Sklárny Poděbrady" → „Poděbrady" (Sklárny = závod). || Poděbrady = Jiskra Poděbrady / HC Poděbrady (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Nymburk). Sklarny Podebrady = sklarsky podnik. Patterns: Sokol -&gt; DSO Jiskra -&gt; TJ Jiskra Poděbrady. city Poděbrady.</t>
-        </is>
-      </c>
-      <c r="J471" t="inlineStr">
-        <is>
-          <t>Poděbrady</t>
-        </is>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>CLUB_S1995_96_0319</t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>čtvrtfinále</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>čtvrtfinále</t>
-        </is>
-      </c>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>30VYCH</t>
-        </is>
-      </c>
-      <c r="F472" t="inlineStr">
-        <is>
-          <t>L100</t>
-        </is>
-      </c>
-      <c r="I472" t="inlineStr">
         <is>
           <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
@@ -47168,7 +47264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -47222,12 +47318,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0003</t>
+          <t>CLUB_S1995_96_0012</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47242,12 +47338,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0012</t>
+          <t>CLUB_S1995_96_0023</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47262,12 +47358,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0015</t>
+          <t>CLUB_S1995_96_0024</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47282,12 +47378,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0023</t>
+          <t>CLUB_S1995_96_0047</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47302,12 +47398,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0024</t>
+          <t>CLUB_S1995_96_0066</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47322,12 +47418,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0030</t>
+          <t>CLUB_S1995_96_0070</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0307 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -47342,12 +47438,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0047</t>
+          <t>CLUB_S1995_96_0075</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0080 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -47362,12 +47458,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0050</t>
+          <t>CLUB_S1995_96_0078</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0100 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -47382,12 +47478,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0066</t>
+          <t>CLUB_S1995_96_0104</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0107 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -47402,12 +47498,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0070</t>
+          <t>CLUB_S1995_96_0159</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0307 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47422,12 +47518,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0075</t>
+          <t>CLUB_S1995_96_0177</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0080 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47442,12 +47538,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0078</t>
+          <t>CLUB_S1995_96_0182</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0100 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47462,12 +47558,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0104</t>
+          <t>CLUB_S1995_96_0183</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0107 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47482,12 +47578,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0159</t>
+          <t>CLUB_S1995_96_0207</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47502,12 +47598,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0159</t>
+          <t>CLUB_S1995_96_0255</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -47522,12 +47618,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0160</t>
+          <t>CLUB_S1995_96_0256</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47542,12 +47638,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0171</t>
+          <t>CLUB_S1995_96_0258</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47562,12 +47658,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0176</t>
+          <t>CLUB_S1995_96_0260</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0173 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -47582,12 +47678,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0177</t>
+          <t>CLUB_S1995_96_0262</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -47602,12 +47698,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0182</t>
+          <t>CLUB_S1995_96_0266</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -47622,12 +47718,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0183</t>
+          <t>CLUB_S1995_96_0269</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47642,12 +47738,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0207</t>
+          <t>CLUB_S1995_96_0303</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'IPF 90 Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47662,12 +47758,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0255</t>
+          <t>CLUB_S1995_96_0329</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47682,12 +47778,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0256</t>
+          <t>CLUB_S1995_96_0380</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0277 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -47702,12 +47798,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0258</t>
+          <t>CLUB_S1995_96_0390</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0237 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -47722,12 +47818,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0260</t>
+          <t>CLUB_S1995_96_0405</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0173 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47742,12 +47838,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0262</t>
+          <t>CLUB_S1995_96_0406</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47762,12 +47858,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0266</t>
+          <t>CLUB_S1995_96_0414</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0311 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -47782,12 +47878,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0269</t>
+          <t>CLUB_S1995_96_0423</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -47802,12 +47898,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0303</t>
+          <t>CLUB_S1995_96_0428</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'IPF 90 Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0322 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -47822,12 +47918,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0329</t>
+          <t>CLUB_S1995_96_0439</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Las Vegas Krnov' → 'Krnov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47842,12 +47938,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0380</t>
+          <t>CLUB_S1995_96_0459</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0277 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Newvers Rangers Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47862,12 +47958,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0390</t>
+          <t>CLUB_S1995_96_0462</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0237 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47882,12 +47978,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0405</t>
+          <t>CLUB_S1995_96_0465</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Sport club Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47902,12 +47998,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0406</t>
+          <t>CLUB_S1995_96_0483</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -47922,12 +48018,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0414</t>
+          <t>CLUB_S1995_96_0483</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0311 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -47942,12 +48038,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0423</t>
+          <t>CLUB_S1995_96_0484</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Holešák Havlíčkův Brod' → 'Havlíčkův Brod' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -47962,197 +48058,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLUB_S1995_96_0428</t>
+          <t>CLUB_S1995_96_0319</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0322 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CLUB_S1995_96_0439</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Las Vegas Krnov' → 'Krnov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CLUB_S1995_96_0453</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CLUB_S1995_96_0459</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Newvers Rangers Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S1995_96_0462</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S1995_96_0465</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Sport club Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CLUB_S1995_96_0483</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CLUB_S1995_96_0483</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CLUB_S1995_96_0484</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Holešák Havlíčkův Brod' → 'Havlíčkův Brod' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>CLUB_S1995_96_0319</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
           <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F48"/>
+  <autoFilter ref="A1:F39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1995_96_FINAL.xlsx
+++ b/data/S1995_96_FINAL.xlsx
@@ -757,7 +757,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -1069,7 +1069,7 @@
         <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H9" t="n">
         <v>6</v>
@@ -1147,7 +1147,7 @@
         <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
@@ -1225,13 +1225,13 @@
         <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
         <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J11" t="n">
         <v>112</v>
@@ -1303,7 +1303,7 @@
         <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" t="n">
         <v>5</v>
@@ -1381,13 +1381,13 @@
         <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H13" t="n">
         <v>11</v>
       </c>
       <c r="I13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J13" t="n">
         <v>105</v>
@@ -1465,7 +1465,7 @@
         <v>9</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
         <v>115</v>
@@ -1543,7 +1543,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
         <v>103</v>
@@ -1620,7 +1620,7 @@
         <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H16" t="n">
         <v>6</v>
@@ -1704,7 +1704,7 @@
         <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
         <v>103</v>
@@ -1781,7 +1781,7 @@
         <v>40</v>
       </c>
       <c r="G18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H18" t="n">
         <v>5</v>
@@ -2477,13 +2477,19 @@
       <c r="I37" t="n">
         <v>3</v>
       </c>
+      <c r="J37" t="n">
+        <v>47</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>47</v>
+        <v>38</v>
+      </c>
+      <c r="M37" t="n">
+        <v>17</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -2549,13 +2555,19 @@
       <c r="I38" t="n">
         <v>4</v>
       </c>
+      <c r="J38" t="n">
+        <v>66</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>66</v>
+        <v>35</v>
+      </c>
+      <c r="M38" t="n">
+        <v>16</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -2626,13 +2638,19 @@
       <c r="I39" t="n">
         <v>5</v>
       </c>
+      <c r="J39" t="n">
+        <v>38</v>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>38</v>
+        <v>46</v>
+      </c>
+      <c r="M39" t="n">
+        <v>12</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -2698,13 +2716,19 @@
       <c r="I40" t="n">
         <v>10</v>
       </c>
+      <c r="J40" t="n">
+        <v>26</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>26</v>
+        <v>58</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>

--- a/data/S1995_96_FINAL.xlsx
+++ b/data/S1995_96_FINAL.xlsx
@@ -48521,7 +48521,7 @@
         <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>129</v>
       </c>
       <c r="M15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -49319,7 +49319,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="M16" t="n">
         <v>27</v>
@@ -50169,7 +50169,7 @@
         <v>4</v>
       </c>
       <c r="J35" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -50631,7 +50631,7 @@
         <v>21</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
@@ -51433,7 +51433,7 @@
         <v>110</v>
       </c>
       <c r="M14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -51516,7 +51516,7 @@
         <v>110</v>
       </c>
       <c r="M15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         <v>125</v>
       </c>
       <c r="M27" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>110</v>
       </c>
       <c r="M34" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -53138,7 +53138,7 @@
         <v>185</v>
       </c>
       <c r="M36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>

--- a/data/S1995_96_FINAL.xlsx
+++ b/data/S1995_96_FINAL.xlsx
@@ -19855,7 +19855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:N105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19919,6 +19919,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23980,8 +23990,6 @@
         </is>
       </c>
     </row>
-    <row r="92"/>
-    <row r="93"/>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
@@ -24111,7 +24119,6 @@
         </is>
       </c>
     </row>
-    <row r="101"/>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>

--- a/data/S1995_96_FINAL.xlsx
+++ b/data/S1995_96_FINAL.xlsx
@@ -20107,6 +20107,16 @@
           <t>NODE_S1995_96_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0010</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0016</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20121,6 +20131,14 @@
         <is>
           <t>NODE_S1994_95_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -20295,6 +20313,16 @@
           <t>NODE_S1995_96_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0019</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20309,6 +20337,14 @@
         <is>
           <t>NODE_S1994_95_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -20384,6 +20420,16 @@
           <t>NODE_S1995_96_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0019</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20398,6 +20444,14 @@
         <is>
           <t>NODE_S1994_95_0009</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -20431,6 +20485,16 @@
           <t>NODE_S1995_96_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0015</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0014</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20445,6 +20509,14 @@
         <is>
           <t>NODE_S1994_95_0010</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -20478,6 +20550,8 @@
           <t>NODE_S1995_96_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20492,6 +20566,14 @@
         <is>
           <t>NODE_S1994_95_0011</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -20525,6 +20607,8 @@
           <t>NODE_S1995_96_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20539,6 +20623,14 @@
         <is>
           <t>NODE_S1994_95_0012</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -20572,6 +20664,8 @@
           <t>NODE_S1995_96_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20586,6 +20680,14 @@
         <is>
           <t>NODE_S1994_95_0013</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -20619,6 +20721,8 @@
           <t>NODE_S1995_96_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20633,6 +20737,14 @@
         <is>
           <t>NODE_S1994_95_0014</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -20666,6 +20778,8 @@
           <t>NODE_S1995_96_0001</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20680,6 +20794,14 @@
         <is>
           <t>NODE_S1994_95_0015</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -20713,6 +20835,8 @@
           <t>NODE_S1995_96_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20727,6 +20851,14 @@
         <is>
           <t>NODE_S1994_95_0016</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -20760,6 +20892,8 @@
           <t>NODE_S1995_96_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20774,6 +20908,14 @@
         <is>
           <t>NODE_S1994_95_0017</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -20807,6 +20949,16 @@
           <t>NODE_S1995_96_0007</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0012</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20821,6 +20973,14 @@
         <is>
           <t>NODE_S1994_95_0018</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -20948,6 +21108,12 @@
           <t>NODE_S1995_96_0003</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20962,6 +21128,14 @@
         <is>
           <t>NODE_S1994_95_0021</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -20995,6 +21169,12 @@
           <t>NODE_S1995_96_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21004,6 +21184,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -21037,6 +21225,12 @@
           <t>NODE_S1995_96_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21051,6 +21245,14 @@
         <is>
           <t>NODE_S1994_95_0023</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -21084,6 +21286,12 @@
           <t>NODE_S1995_96_0003</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21098,6 +21306,14 @@
         <is>
           <t>NODE_S1994_95_0024</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -21131,6 +21347,8 @@
           <t>NODE_S1995_96_0003</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21140,6 +21358,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -21403,6 +21629,8 @@
           <t>NODE_S1995_96_0029</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21412,6 +21640,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -21487,6 +21723,8 @@
           <t>NODE_S1995_96_0029</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21496,6 +21734,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -21670,6 +21916,8 @@
           <t>NODE_S1995_96_0035</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21684,6 +21932,14 @@
         <is>
           <t>NODE_S1994_95_0034</t>
         </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -22115,6 +22371,8 @@
           <t>NODE_S1995_96_0041</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22124,6 +22382,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -22157,6 +22423,8 @@
           <t>NODE_S1995_96_0041</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22166,6 +22434,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -22199,6 +22475,8 @@
           <t>NODE_S1995_96_0041</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22208,6 +22486,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -22335,6 +22621,12 @@
           <t>NODE_S1995_96_0051</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0054</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22349,6 +22641,14 @@
         <is>
           <t>NODE_S1994_95_0043</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -22382,6 +22682,8 @@
           <t>NODE_S1995_96_0051</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22391,6 +22693,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -23178,6 +23488,8 @@
           <t>NODE_S1995_96_0068</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23187,6 +23499,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -23450,6 +23770,8 @@
           <t>NODE_S1995_96_0068</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23459,6 +23781,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="80">
@@ -23492,6 +23822,8 @@
           <t>NODE_S1995_96_0068</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23501,6 +23833,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -23534,6 +23874,8 @@
           <t>NODE_S1995_96_0068</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23543,6 +23885,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -23576,6 +23926,8 @@
           <t>NODE_S1995_96_0068</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23585,6 +23937,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -23618,6 +23978,8 @@
           <t>NODE_S1995_96_0068</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23627,6 +23989,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -23660,6 +24030,8 @@
           <t>NODE_S1995_96_0068</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23669,6 +24041,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -23697,6 +24077,12 @@
           <t>REG_SVM</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0089</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23716,6 +24102,14 @@
         <is>
           <t>NODE_S1994_95_0079</t>
         </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -23932,6 +24326,8 @@
           <t>NODE_S1995_96_0084</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23941,6 +24337,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -23974,6 +24378,8 @@
           <t>NODE_S1995_96_0084</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23989,7 +24395,17 @@
           <t>NODE_S1994_95_0086</t>
         </is>
       </c>
-    </row>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92"/>
+    <row r="93"/>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
@@ -24119,6 +24535,7 @@
         </is>
       </c>
     </row>
+    <row r="101"/>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>

--- a/data/S1995_96_FINAL.xlsx
+++ b/data/S1995_96_FINAL.xlsx
@@ -831,6 +831,11 @@
           <t>HC Petra Vsetín (C)</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F6" t="n">
         <v>40</v>
       </c>
@@ -20550,8 +20555,6 @@
           <t>NODE_S1995_96_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20607,8 +20610,6 @@
           <t>NODE_S1995_96_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20664,8 +20665,6 @@
           <t>NODE_S1995_96_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20721,8 +20720,6 @@
           <t>NODE_S1995_96_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20778,8 +20775,6 @@
           <t>NODE_S1995_96_0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20835,8 +20830,6 @@
           <t>NODE_S1995_96_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20892,8 +20885,6 @@
           <t>NODE_S1995_96_0007</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21113,7 +21104,6 @@
           <t>NODE_S1995_96_0023</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21174,7 +21164,6 @@
           <t>NODE_S1995_96_0024</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21230,7 +21219,6 @@
           <t>NODE_S1995_96_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21291,7 +21279,6 @@
           <t>NODE_S1995_96_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21347,8 +21334,6 @@
           <t>NODE_S1995_96_0003</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21629,8 +21614,6 @@
           <t>NODE_S1995_96_0029</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21723,8 +21706,6 @@
           <t>NODE_S1995_96_0029</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21916,8 +21897,6 @@
           <t>NODE_S1995_96_0035</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22371,8 +22350,6 @@
           <t>NODE_S1995_96_0041</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22423,8 +22400,6 @@
           <t>NODE_S1995_96_0041</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22475,8 +22450,6 @@
           <t>NODE_S1995_96_0041</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22626,7 +22599,6 @@
           <t>NODE_S1995_96_0054</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22682,8 +22654,6 @@
           <t>NODE_S1995_96_0051</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23488,8 +23458,6 @@
           <t>NODE_S1995_96_0068</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23770,8 +23738,6 @@
           <t>NODE_S1995_96_0068</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23822,8 +23788,6 @@
           <t>NODE_S1995_96_0068</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23874,8 +23838,6 @@
           <t>NODE_S1995_96_0068</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23926,8 +23888,6 @@
           <t>NODE_S1995_96_0068</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23978,8 +23938,6 @@
           <t>NODE_S1995_96_0068</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24030,8 +23988,6 @@
           <t>NODE_S1995_96_0068</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24082,7 +24038,6 @@
           <t>NODE_S1995_96_0089</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24326,8 +24281,6 @@
           <t>NODE_S1995_96_0084</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24378,8 +24331,6 @@
           <t>NODE_S1995_96_0084</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24404,8 +24355,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92"/>
-    <row r="93"/>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
@@ -24535,7 +24484,6 @@
         </is>
       </c>
     </row>
-    <row r="101"/>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
@@ -47450,7 +47398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47698,6 +47646,18 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>Zdrojový konflikt: Karlovy Vary v 1. lize GF 149 vs PDF 145. Ponecháno jako otevřený konflikt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HC Petra Vsetín</t>
         </is>
       </c>
     </row>

--- a/data/S1995_96_FINAL.xlsx
+++ b/data/S1995_96_FINAL.xlsx
@@ -24355,6 +24355,8 @@
         <v>5</v>
       </c>
     </row>
+    <row r="92"/>
+    <row r="93"/>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
@@ -24484,6 +24486,7 @@
         </is>
       </c>
     </row>
+    <row r="101"/>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>

--- a/data/S1995_96_FINAL.xlsx
+++ b/data/S1995_96_FINAL.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,8 +55,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +87,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -96,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -108,6 +117,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -30000,8 +30011,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92"/>
-    <row r="93"/>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
@@ -30131,7 +30140,6 @@
         </is>
       </c>
     </row>
-    <row r="101"/>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
@@ -61678,7 +61686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -61735,7 +61743,7 @@
           <t>CLUB_S1995_96_0012</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61755,7 +61763,7 @@
           <t>CLUB_S1995_96_0023</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61775,7 +61783,7 @@
           <t>CLUB_S1995_96_0024</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61795,7 +61803,7 @@
           <t>CLUB_S1995_96_0047</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61815,7 +61823,7 @@
           <t>CLUB_S1995_96_0066</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61835,7 +61843,7 @@
           <t>CLUB_S1995_96_0070</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0307 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -61855,7 +61863,7 @@
           <t>CLUB_S1995_96_0075</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0080 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -61875,7 +61883,7 @@
           <t>CLUB_S1995_96_0078</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0100 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -61895,7 +61903,7 @@
           <t>CLUB_S1995_96_0104</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0107 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -61915,7 +61923,7 @@
           <t>CLUB_S1995_96_0159</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61935,7 +61943,7 @@
           <t>CLUB_S1995_96_0177</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61955,7 +61963,7 @@
           <t>CLUB_S1995_96_0182</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61975,7 +61983,7 @@
           <t>CLUB_S1995_96_0183</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61995,7 +62003,7 @@
           <t>CLUB_S1995_96_0207</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -62015,7 +62023,7 @@
           <t>CLUB_S1995_96_0255</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -62035,7 +62043,7 @@
           <t>CLUB_S1995_96_0256</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -62055,7 +62063,7 @@
           <t>CLUB_S1995_96_0258</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -62075,7 +62083,7 @@
           <t>CLUB_S1995_96_0260</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0173 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -62095,7 +62103,7 @@
           <t>CLUB_S1995_96_0262</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -62115,7 +62123,7 @@
           <t>CLUB_S1995_96_0266</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -62135,7 +62143,7 @@
           <t>CLUB_S1995_96_0269</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -62155,7 +62163,7 @@
           <t>CLUB_S1995_96_0303</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: city 'IPF 90 Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -62175,7 +62183,7 @@
           <t>CLUB_S1995_96_0329</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -62195,7 +62203,7 @@
           <t>CLUB_S1995_96_0380</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0277 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -62215,7 +62223,7 @@
           <t>CLUB_S1995_96_0390</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0237 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -62235,7 +62243,7 @@
           <t>CLUB_S1995_96_0405</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -62255,7 +62263,7 @@
           <t>CLUB_S1995_96_0406</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -62275,7 +62283,7 @@
           <t>CLUB_S1995_96_0414</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0311 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -62295,7 +62303,7 @@
           <t>CLUB_S1995_96_0423</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -62315,7 +62323,7 @@
           <t>CLUB_S1995_96_0428</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0322 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -62335,7 +62343,7 @@
           <t>CLUB_S1995_96_0439</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>TBD: city 'Las Vegas Krnov' → 'Krnov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -62355,7 +62363,7 @@
           <t>CLUB_S1995_96_0459</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>TBD: city 'Newvers Rangers Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -62375,7 +62383,7 @@
           <t>CLUB_S1995_96_0462</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -62395,7 +62403,7 @@
           <t>CLUB_S1995_96_0465</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>TBD: city 'Sport club Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -62415,7 +62423,7 @@
           <t>CLUB_S1995_96_0483</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -62435,7 +62443,7 @@
           <t>CLUB_S1995_96_0483</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1994_95_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -62455,7 +62463,7 @@
           <t>CLUB_S1995_96_0484</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>TBD: city 'Holešák Havlíčkův Brod' → 'Havlíčkův Brod' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -62475,11 +62483,63 @@
           <t>CLUB_S1995_96_0319</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>30_Středočeský L40  (Středočeský kraj) · NODE_S1995_96_0045</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (HC Benešov (N2), HC Řevnice „B“ (N2)), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Východočeský – Pardubice / 4. (východní Čechy) · NODE_S1995_96_0096</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (Havl.Brod), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F39"/>
